--- a/Output Data Tables/APAT Outputs/Aggregated Tables/2023/Aircraft_Cumulative_Statistics_2023.xlsx
+++ b/Output Data Tables/APAT Outputs/Aggregated Tables/2023/Aircraft_Cumulative_Statistics_2023.xlsx
@@ -13,78 +13,117 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="36" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="49" uniqueCount="49">
   <si>
     <t>Row</t>
   </si>
   <si>
-    <t>Alaska</t>
-  </si>
-  <si>
-    <t>Allegiant</t>
-  </si>
-  <si>
-    <t>American</t>
-  </si>
-  <si>
-    <t>Breeze</t>
-  </si>
-  <si>
-    <t>Delta</t>
-  </si>
-  <si>
-    <t>Frontier</t>
-  </si>
-  <si>
-    <t>Hawaiian</t>
-  </si>
-  <si>
-    <t>JetBlue</t>
-  </si>
-  <si>
-    <t>Southwest</t>
-  </si>
-  <si>
-    <t>Spirit</t>
-  </si>
-  <si>
-    <t>Sun Country</t>
-  </si>
-  <si>
-    <t>United</t>
-  </si>
-  <si>
-    <t>CommuteAir</t>
-  </si>
-  <si>
-    <t>Endeavor</t>
-  </si>
-  <si>
-    <t>Envoy</t>
-  </si>
-  <si>
-    <t>GoJet</t>
-  </si>
-  <si>
-    <t>Horizon</t>
-  </si>
-  <si>
-    <t>Mesa</t>
-  </si>
-  <si>
-    <t>Piedmont</t>
-  </si>
-  <si>
-    <t>PSA</t>
-  </si>
-  <si>
-    <t>Republic</t>
-  </si>
-  <si>
-    <t>SkyWest</t>
-  </si>
-  <si>
-    <t>All Airlines</t>
+    <t>E145</t>
+  </si>
+  <si>
+    <t>CRJ-200</t>
+  </si>
+  <si>
+    <t>E170</t>
+  </si>
+  <si>
+    <t>E175</t>
+  </si>
+  <si>
+    <t>CRJ-500</t>
+  </si>
+  <si>
+    <t>CRJ-700</t>
+  </si>
+  <si>
+    <t>E190</t>
+  </si>
+  <si>
+    <t>CRJ-900</t>
+  </si>
+  <si>
+    <t>A220-100</t>
+  </si>
+  <si>
+    <t>A220-300</t>
+  </si>
+  <si>
+    <t>A319</t>
+  </si>
+  <si>
+    <t>A320</t>
+  </si>
+  <si>
+    <t>A320NEO</t>
+  </si>
+  <si>
+    <t>A321</t>
+  </si>
+  <si>
+    <t>A321NEO</t>
+  </si>
+  <si>
+    <t>B717-200</t>
+  </si>
+  <si>
+    <t>B737-700</t>
+  </si>
+  <si>
+    <t>B737-800</t>
+  </si>
+  <si>
+    <t>B737-8</t>
+  </si>
+  <si>
+    <t>B737-900</t>
+  </si>
+  <si>
+    <t>B737-900ER</t>
+  </si>
+  <si>
+    <t>B737-9</t>
+  </si>
+  <si>
+    <t>B757-200</t>
+  </si>
+  <si>
+    <t>B757-300</t>
+  </si>
+  <si>
+    <t>B767-300</t>
+  </si>
+  <si>
+    <t>B767-400</t>
+  </si>
+  <si>
+    <t>A330-200</t>
+  </si>
+  <si>
+    <t>A330-300</t>
+  </si>
+  <si>
+    <t>A330-900</t>
+  </si>
+  <si>
+    <t>A350-900</t>
+  </si>
+  <si>
+    <t>B787-8</t>
+  </si>
+  <si>
+    <t>B787-9</t>
+  </si>
+  <si>
+    <t>B787-10</t>
+  </si>
+  <si>
+    <t>B777-200</t>
+  </si>
+  <si>
+    <t>B777-300</t>
+  </si>
+  <si>
+    <t>All Aircraft</t>
   </si>
   <si>
     <t>RPMs</t>
@@ -166,10 +205,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:M24"/>
+  <dimension ref="A1:M37"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="12.42578125" customWidth="true"/>
+    <col min="1" max="1" width="11.140625" customWidth="true"/>
     <col min="2" max="2" width="15.85546875" customWidth="true"/>
     <col min="3" max="3" width="15.85546875" customWidth="true"/>
     <col min="4" max="4" width="13.140625" customWidth="true"/>
@@ -189,40 +228,40 @@
         <v>0</v>
       </c>
       <c r="B1" s="0" t="s">
-        <v>24</v>
+        <v>37</v>
       </c>
       <c r="C1" s="0" t="s">
-        <v>25</v>
+        <v>38</v>
       </c>
       <c r="D1" s="0" t="s">
-        <v>26</v>
+        <v>39</v>
       </c>
       <c r="E1" s="0" t="s">
-        <v>27</v>
+        <v>40</v>
       </c>
       <c r="F1" s="0" t="s">
-        <v>28</v>
+        <v>41</v>
       </c>
       <c r="G1" s="0" t="s">
-        <v>29</v>
+        <v>42</v>
       </c>
       <c r="H1" s="0" t="s">
-        <v>30</v>
+        <v>43</v>
       </c>
       <c r="I1" s="0" t="s">
-        <v>31</v>
+        <v>44</v>
       </c>
       <c r="J1" s="0" t="s">
-        <v>32</v>
+        <v>45</v>
       </c>
       <c r="K1" s="0" t="s">
-        <v>33</v>
+        <v>46</v>
       </c>
       <c r="L1" s="0" t="s">
-        <v>34</v>
+        <v>47</v>
       </c>
       <c r="M1" s="0" t="s">
-        <v>35</v>
+        <v>48</v>
       </c>
     </row>
     <row r="2">
@@ -230,40 +269,40 @@
         <v>1</v>
       </c>
       <c r="B2" s="0">
-        <v>52978082349</v>
+        <v>2678843025</v>
       </c>
       <c r="C2" s="0">
-        <v>63335188948</v>
+        <v>3164679184</v>
       </c>
       <c r="D2" s="0">
-        <v>786968</v>
+        <v>66751</v>
       </c>
       <c r="E2" s="0">
-        <v>169</v>
+        <v>50</v>
       </c>
       <c r="F2" s="0">
-        <v>261526</v>
+        <v>188384</v>
       </c>
       <c r="G2" s="0">
-        <v>3.25</v>
+        <v>3.9700000000000002</v>
       </c>
       <c r="H2" s="0">
-        <v>11.4</v>
+        <v>5.8700000000000001</v>
       </c>
       <c r="I2" s="0">
-        <v>83.650000000000006</v>
+        <v>84.650000000000006</v>
       </c>
       <c r="J2" s="0">
-        <v>1407</v>
+        <v>336</v>
       </c>
       <c r="K2" s="0">
-        <v>4984</v>
+        <v>2050.8800000000001</v>
       </c>
       <c r="L2" s="0">
-        <v>29.039999999999999</v>
+        <v>41.020000000000003</v>
       </c>
       <c r="M2" s="0">
-        <v>0.070000000000000007</v>
+        <v>0.17999999999999999</v>
       </c>
     </row>
     <row r="3">
@@ -271,40 +310,40 @@
         <v>2</v>
       </c>
       <c r="B3" s="0">
-        <v>15934620409</v>
+        <v>1611785435</v>
       </c>
       <c r="C3" s="0">
-        <v>18461299152</v>
+        <v>2115281440</v>
       </c>
       <c r="D3" s="0">
-        <v>403879</v>
+        <v>36208</v>
       </c>
       <c r="E3" s="0">
-        <v>176</v>
+        <v>50</v>
       </c>
       <c r="F3" s="0">
-        <v>116285</v>
+        <v>126026</v>
       </c>
       <c r="G3" s="0">
-        <v>2.54</v>
+        <v>2.1600000000000001</v>
       </c>
       <c r="H3" s="0">
-        <v>6.1100000000000003</v>
+        <v>3.0299999999999998</v>
       </c>
       <c r="I3" s="0">
-        <v>86.310000000000002</v>
+        <v>76.200000000000003</v>
       </c>
       <c r="J3" s="0">
-        <v>898</v>
+        <v>336</v>
       </c>
       <c r="K3" s="0">
-        <v>5312</v>
+        <v>2480.46</v>
       </c>
       <c r="L3" s="0">
-        <v>30.09</v>
+        <v>49.609999999999999</v>
       </c>
       <c r="M3" s="0">
-        <v>0.080000000000000002</v>
+        <v>0.20799999999999999</v>
       </c>
     </row>
     <row r="4">
@@ -312,40 +351,40 @@
         <v>3</v>
       </c>
       <c r="B4" s="0">
-        <v>209674168843</v>
+        <v>1685606282</v>
       </c>
       <c r="C4" s="0">
-        <v>249800534127</v>
+        <v>2002685392</v>
       </c>
       <c r="D4" s="0">
-        <v>728154</v>
+        <v>57681</v>
       </c>
       <c r="E4" s="0">
-        <v>174</v>
+        <v>68</v>
       </c>
       <c r="F4" s="0">
-        <v>1144745</v>
+        <v>62276</v>
       </c>
       <c r="G4" s="0">
-        <v>3.3399999999999999</v>
+        <v>1.79</v>
       </c>
       <c r="H4" s="0">
-        <v>9.9100000000000001</v>
+        <v>3.1699999999999999</v>
       </c>
       <c r="I4" s="0">
-        <v>83.939999999999998</v>
+        <v>84.170000000000002</v>
       </c>
       <c r="J4" s="0">
-        <v>1147</v>
+        <v>475</v>
       </c>
       <c r="K4" s="0">
-        <v>7173</v>
+        <v>1884.53</v>
       </c>
       <c r="L4" s="0">
-        <v>38.700000000000003</v>
+        <v>27.82</v>
       </c>
       <c r="M4" s="0">
-        <v>0.10000000000000001</v>
+        <v>0.104</v>
       </c>
     </row>
     <row r="5">
@@ -353,40 +392,40 @@
         <v>4</v>
       </c>
       <c r="B5" s="0">
-        <v>2199500539</v>
+        <v>31343967901</v>
       </c>
       <c r="C5" s="0">
-        <v>2864472677</v>
+        <v>38536746923</v>
       </c>
       <c r="D5" s="0">
-        <v>65535</v>
+        <v>128808</v>
       </c>
       <c r="E5" s="0">
-        <v>129</v>
+        <v>75</v>
       </c>
       <c r="F5" s="0">
-        <v>21918</v>
+        <v>997537</v>
       </c>
       <c r="G5" s="0">
-        <v>65535</v>
+        <v>3.3300000000000001</v>
       </c>
       <c r="H5" s="0">
-        <v>65535</v>
+        <v>5.9699999999999998</v>
       </c>
       <c r="I5" s="0">
-        <v>76.790000000000006</v>
+        <v>81.340000000000003</v>
       </c>
       <c r="J5" s="0">
-        <v>1003</v>
+        <v>514</v>
       </c>
       <c r="K5" s="0">
-        <v>0</v>
+        <v>1692.8299999999999</v>
       </c>
       <c r="L5" s="0">
-        <v>0</v>
+        <v>22.550000000000001</v>
       </c>
       <c r="M5" s="0">
-        <v>0</v>
+        <v>0.079000000000000001</v>
       </c>
     </row>
     <row r="6">
@@ -394,40 +433,40 @@
         <v>5</v>
       </c>
       <c r="B6" s="0">
-        <v>219276285138</v>
+        <v>606963891</v>
       </c>
       <c r="C6" s="0">
-        <v>256187557373</v>
+        <v>735124450</v>
       </c>
       <c r="D6" s="0">
-        <v>767373</v>
+        <v>30066</v>
       </c>
       <c r="E6" s="0">
-        <v>170</v>
+        <v>50</v>
       </c>
       <c r="F6" s="0">
-        <v>1118899</v>
+        <v>45438</v>
       </c>
       <c r="G6" s="0">
-        <v>3.3500000000000001</v>
+        <v>1.8600000000000001</v>
       </c>
       <c r="H6" s="0">
-        <v>10.02</v>
+        <v>2.8100000000000001</v>
       </c>
       <c r="I6" s="0">
-        <v>85.590000000000003</v>
+        <v>82.569999999999993</v>
       </c>
       <c r="J6" s="0">
-        <v>1184</v>
+        <v>324</v>
       </c>
       <c r="K6" s="0">
-        <v>6592</v>
+        <v>2810.73</v>
       </c>
       <c r="L6" s="0">
-        <v>35.140000000000001</v>
+        <v>56.210000000000001</v>
       </c>
       <c r="M6" s="0">
-        <v>0.089999999999999997</v>
+        <v>0.26200000000000001</v>
       </c>
     </row>
     <row r="7">
@@ -435,40 +474,40 @@
         <v>6</v>
       </c>
       <c r="B7" s="0">
-        <v>30768436678</v>
+        <v>4811058348</v>
       </c>
       <c r="C7" s="0">
-        <v>37784345072</v>
+        <v>6121509112</v>
       </c>
       <c r="D7" s="0">
-        <v>818197</v>
+        <v>89222</v>
       </c>
       <c r="E7" s="0">
-        <v>199</v>
+        <v>66</v>
       </c>
       <c r="F7" s="0">
-        <v>188843</v>
+        <v>216349</v>
       </c>
       <c r="G7" s="0">
-        <v>4.0899999999999999</v>
+        <v>3.1499999999999999</v>
       </c>
       <c r="H7" s="0">
-        <v>11.33</v>
+        <v>5.0800000000000001</v>
       </c>
       <c r="I7" s="0">
-        <v>81.430000000000007</v>
+        <v>78.590000000000003</v>
       </c>
       <c r="J7" s="0">
-        <v>1006</v>
+        <v>428</v>
       </c>
       <c r="K7" s="0">
-        <v>4902</v>
+        <v>2567.5900000000001</v>
       </c>
       <c r="L7" s="0">
-        <v>24.640000000000001</v>
+        <v>38.890000000000001</v>
       </c>
       <c r="M7" s="0">
-        <v>0.070000000000000007</v>
+        <v>0.14599999999999999</v>
       </c>
     </row>
     <row r="8">
@@ -476,40 +515,40 @@
         <v>7</v>
       </c>
       <c r="B8" s="0">
-        <v>16861017055</v>
+        <v>3328424207</v>
       </c>
       <c r="C8" s="0">
-        <v>20198057398</v>
+        <v>4120279832</v>
       </c>
       <c r="D8" s="0">
-        <v>905742</v>
+        <v>236119</v>
       </c>
       <c r="E8" s="0">
-        <v>165</v>
+        <v>101</v>
       </c>
       <c r="F8" s="0">
-        <v>84105</v>
+        <v>81316</v>
       </c>
       <c r="G8" s="0">
-        <v>3.77</v>
+        <v>4.6600000000000001</v>
       </c>
       <c r="H8" s="0">
-        <v>9.4600000000000009</v>
+        <v>8.3399999999999999</v>
       </c>
       <c r="I8" s="0">
-        <v>83.480000000000004</v>
+        <v>80.780000000000001</v>
       </c>
       <c r="J8" s="0">
-        <v>1009</v>
+        <v>503</v>
       </c>
       <c r="K8" s="0">
-        <v>8113</v>
+        <v>5513.1599999999999</v>
       </c>
       <c r="L8" s="0">
-        <v>36.380000000000003</v>
+        <v>54.789999999999999</v>
       </c>
       <c r="M8" s="0">
-        <v>0.080000000000000002</v>
+        <v>0.19500000000000001</v>
       </c>
     </row>
     <row r="9">
@@ -517,40 +556,40 @@
         <v>8</v>
       </c>
       <c r="B9" s="0">
-        <v>56776931776</v>
+        <v>10990857295</v>
       </c>
       <c r="C9" s="0">
-        <v>68537979627</v>
+        <v>13435631377</v>
       </c>
       <c r="D9" s="0">
-        <v>662395</v>
+        <v>145156</v>
       </c>
       <c r="E9" s="0">
-        <v>151</v>
+        <v>75</v>
       </c>
       <c r="F9" s="0">
-        <v>348368</v>
+        <v>415846</v>
       </c>
       <c r="G9" s="0">
-        <v>3.3700000000000001</v>
+        <v>4.4900000000000002</v>
       </c>
       <c r="H9" s="0">
-        <v>10.83</v>
+        <v>7.2699999999999996</v>
       </c>
       <c r="I9" s="0">
-        <v>82.840000000000003</v>
+        <v>81.799999999999997</v>
       </c>
       <c r="J9" s="0">
-        <v>1227</v>
+        <v>429</v>
       </c>
       <c r="K9" s="0">
-        <v>5396</v>
+        <v>2096.96</v>
       </c>
       <c r="L9" s="0">
-        <v>34.119999999999997</v>
+        <v>27.82</v>
       </c>
       <c r="M9" s="0">
-        <v>0.089999999999999997</v>
+        <v>0.105</v>
       </c>
     </row>
     <row r="10">
@@ -558,40 +597,40 @@
         <v>9</v>
       </c>
       <c r="B10" s="0">
-        <v>136287720622</v>
+        <v>5042223818</v>
       </c>
       <c r="C10" s="0">
-        <v>170360655398</v>
+        <v>5940796394</v>
       </c>
       <c r="D10" s="0">
-        <v>582888</v>
+        <v>366716</v>
       </c>
       <c r="E10" s="0">
-        <v>159</v>
+        <v>109</v>
       </c>
       <c r="F10" s="0">
-        <v>1459654</v>
+        <v>58208</v>
       </c>
       <c r="G10" s="0">
-        <v>4.9900000000000002</v>
+        <v>3.5899999999999999</v>
       </c>
       <c r="H10" s="0">
-        <v>10.029999999999999</v>
+        <v>9.4800000000000004</v>
       </c>
       <c r="I10" s="0">
-        <v>80</v>
+        <v>84.870000000000005</v>
       </c>
       <c r="J10" s="0">
-        <v>730</v>
+        <v>937</v>
       </c>
       <c r="K10" s="0">
-        <v>4763</v>
+        <v>4983.1599999999999</v>
       </c>
       <c r="L10" s="0">
-        <v>29.850000000000001</v>
+        <v>45.729999999999997</v>
       </c>
       <c r="M10" s="0">
-        <v>0.080000000000000002</v>
+        <v>0.129</v>
       </c>
     </row>
     <row r="11">
@@ -599,40 +638,40 @@
         <v>10</v>
       </c>
       <c r="B11" s="0">
-        <v>45227510940</v>
+        <v>7165334582</v>
       </c>
       <c r="C11" s="0">
-        <v>55635577138</v>
+        <v>8777447933</v>
       </c>
       <c r="D11" s="0">
-        <v>763700</v>
+        <v>707288</v>
       </c>
       <c r="E11" s="0">
-        <v>185</v>
+        <v>134</v>
       </c>
       <c r="F11" s="0">
-        <v>296262</v>
+        <v>58569</v>
       </c>
       <c r="G11" s="0">
-        <v>4.0700000000000003</v>
+        <v>4.7199999999999998</v>
       </c>
       <c r="H11" s="0">
-        <v>11.039999999999999</v>
+        <v>14</v>
       </c>
       <c r="I11" s="0">
-        <v>81.290000000000006</v>
+        <v>81.629999999999995</v>
       </c>
       <c r="J11" s="0">
-        <v>1012</v>
+        <v>1114</v>
       </c>
       <c r="K11" s="0">
-        <v>4715</v>
+        <v>3835.1799999999998</v>
       </c>
       <c r="L11" s="0">
-        <v>25.43</v>
+        <v>28.5</v>
       </c>
       <c r="M11" s="0">
-        <v>0.070000000000000007</v>
+        <v>0.075999999999999998</v>
       </c>
     </row>
     <row r="12">
@@ -640,40 +679,40 @@
         <v>11</v>
       </c>
       <c r="B12" s="0">
-        <v>5865971459</v>
+        <v>38332240832</v>
       </c>
       <c r="C12" s="0">
-        <v>7321550532</v>
+        <v>45966398192</v>
       </c>
       <c r="D12" s="0">
-        <v>370336</v>
+        <v>385592</v>
       </c>
       <c r="E12" s="0">
-        <v>184</v>
+        <v>132</v>
       </c>
       <c r="F12" s="0">
-        <v>35912</v>
+        <v>446753</v>
       </c>
       <c r="G12" s="0">
-        <v>1.8200000000000001</v>
+        <v>3.75</v>
       </c>
       <c r="H12" s="0">
-        <v>5.2599999999999998</v>
+        <v>8.4499999999999993</v>
       </c>
       <c r="I12" s="0">
-        <v>80.120000000000005</v>
+        <v>83.390000000000001</v>
       </c>
       <c r="J12" s="0">
-        <v>1109</v>
+        <v>780</v>
       </c>
       <c r="K12" s="0">
-        <v>5745</v>
+        <v>5238.4399999999996</v>
       </c>
       <c r="L12" s="0">
-        <v>31.25</v>
+        <v>39.780000000000001</v>
       </c>
       <c r="M12" s="0">
-        <v>0.080000000000000002</v>
+        <v>0.115</v>
       </c>
     </row>
     <row r="13">
@@ -681,40 +720,40 @@
         <v>12</v>
       </c>
       <c r="B13" s="0">
-        <v>229916409689</v>
+        <v>83263671726</v>
       </c>
       <c r="C13" s="0">
-        <v>274046492919</v>
+        <v>100304254392</v>
       </c>
       <c r="D13" s="0">
-        <v>825267</v>
+        <v>553311</v>
       </c>
       <c r="E13" s="0">
-        <v>176</v>
+        <v>164</v>
       </c>
       <c r="F13" s="0">
-        <v>910204</v>
+        <v>643900</v>
       </c>
       <c r="G13" s="0">
-        <v>2.7400000000000002</v>
+        <v>3.5499999999999998</v>
       </c>
       <c r="H13" s="0">
-        <v>9.9100000000000001</v>
+        <v>9.1699999999999999</v>
       </c>
       <c r="I13" s="0">
-        <v>83.900000000000006</v>
+        <v>83.010000000000005</v>
       </c>
       <c r="J13" s="0">
-        <v>1491</v>
+        <v>947</v>
       </c>
       <c r="K13" s="0">
-        <v>7233</v>
+        <v>5526.6899999999996</v>
       </c>
       <c r="L13" s="0">
-        <v>37.009999999999998</v>
+        <v>33.659999999999997</v>
       </c>
       <c r="M13" s="0">
-        <v>0.089999999999999997</v>
+        <v>0.091999999999999998</v>
       </c>
     </row>
     <row r="14">
@@ -722,40 +761,40 @@
         <v>13</v>
       </c>
       <c r="B14" s="0">
-        <v>1239243712</v>
+        <v>37390349543</v>
       </c>
       <c r="C14" s="0">
-        <v>1433920400</v>
+        <v>45247127300</v>
       </c>
       <c r="D14" s="0">
-        <v>70846</v>
+        <v>764310</v>
       </c>
       <c r="E14" s="0">
-        <v>50</v>
+        <v>184</v>
       </c>
       <c r="F14" s="0">
-        <v>72175</v>
+        <v>236739</v>
       </c>
       <c r="G14" s="0">
-        <v>3.5699999999999998</v>
+        <v>4</v>
       </c>
       <c r="H14" s="0">
-        <v>5.5199999999999996</v>
+        <v>11.19</v>
       </c>
       <c r="I14" s="0">
-        <v>86.420000000000002</v>
+        <v>82.640000000000001</v>
       </c>
       <c r="J14" s="0">
-        <v>397</v>
+        <v>1038</v>
       </c>
       <c r="K14" s="0">
-        <v>1709</v>
+        <v>4660.0799999999999</v>
       </c>
       <c r="L14" s="0">
-        <v>34.18</v>
+        <v>25.309999999999999</v>
       </c>
       <c r="M14" s="0">
-        <v>0.13</v>
+        <v>0.068000000000000005</v>
       </c>
     </row>
     <row r="15">
@@ -763,40 +802,40 @@
         <v>14</v>
       </c>
       <c r="B15" s="0">
-        <v>5485049614</v>
+        <v>112260940495</v>
       </c>
       <c r="C15" s="0">
-        <v>6729587277</v>
+        <v>132270457295</v>
       </c>
       <c r="D15" s="0">
-        <v>138840</v>
+        <v>796666</v>
       </c>
       <c r="E15" s="0">
-        <v>74</v>
+        <v>192</v>
       </c>
       <c r="F15" s="0">
-        <v>214222</v>
+        <v>609729</v>
       </c>
       <c r="G15" s="0">
-        <v>4.4199999999999999</v>
+        <v>3.6699999999999999</v>
       </c>
       <c r="H15" s="0">
-        <v>7.1200000000000001</v>
+        <v>11.06</v>
       </c>
       <c r="I15" s="0">
-        <v>81.510000000000005</v>
+        <v>84.870000000000005</v>
       </c>
       <c r="J15" s="0">
-        <v>422</v>
+        <v>1156</v>
       </c>
       <c r="K15" s="0">
-        <v>1936</v>
+        <v>6012.0600000000004</v>
       </c>
       <c r="L15" s="0">
-        <v>26.059999999999999</v>
+        <v>31.879999999999999</v>
       </c>
       <c r="M15" s="0">
-        <v>0.10000000000000001</v>
+        <v>0.083000000000000004</v>
       </c>
     </row>
     <row r="16">
@@ -804,40 +843,40 @@
         <v>15</v>
       </c>
       <c r="B16" s="0">
-        <v>7891087096</v>
+        <v>52356590976</v>
       </c>
       <c r="C16" s="0">
-        <v>9674418267</v>
+        <v>62104598448</v>
       </c>
       <c r="D16" s="0">
-        <v>67545</v>
+        <v>976795</v>
       </c>
       <c r="E16" s="0">
-        <v>73</v>
+        <v>200</v>
       </c>
       <c r="F16" s="0">
-        <v>241425</v>
+        <v>175525</v>
       </c>
       <c r="G16" s="0">
-        <v>1.6899999999999999</v>
+        <v>2.7599999999999998</v>
       </c>
       <c r="H16" s="0">
-        <v>3.0499999999999998</v>
+        <v>11.82</v>
       </c>
       <c r="I16" s="0">
-        <v>81.569999999999993</v>
+        <v>84.299999999999997</v>
       </c>
       <c r="J16" s="0">
-        <v>541</v>
+        <v>1808</v>
       </c>
       <c r="K16" s="0">
-        <v>2159</v>
+        <v>6199.8599999999997</v>
       </c>
       <c r="L16" s="0">
-        <v>29.289999999999999</v>
+        <v>31.57</v>
       </c>
       <c r="M16" s="0">
-        <v>0.10000000000000001</v>
+        <v>0.074999999999999997</v>
       </c>
     </row>
     <row r="17">
@@ -845,40 +884,40 @@
         <v>16</v>
       </c>
       <c r="B17" s="0">
-        <v>606963891</v>
+        <v>6343882022</v>
       </c>
       <c r="C17" s="0">
-        <v>735124450</v>
+        <v>7530081594</v>
       </c>
       <c r="D17" s="0">
-        <v>30066</v>
+        <v>232123</v>
       </c>
       <c r="E17" s="0">
-        <v>50</v>
+        <v>116</v>
       </c>
       <c r="F17" s="0">
-        <v>45438</v>
+        <v>186904</v>
       </c>
       <c r="G17" s="0">
-        <v>1.8600000000000001</v>
+        <v>5.7599999999999998</v>
       </c>
       <c r="H17" s="0">
-        <v>2.8100000000000001</v>
+        <v>7.4400000000000004</v>
       </c>
       <c r="I17" s="0">
-        <v>82.569999999999993</v>
+        <v>84.25</v>
       </c>
       <c r="J17" s="0">
-        <v>324</v>
+        <v>359</v>
       </c>
       <c r="K17" s="0">
-        <v>2811</v>
+        <v>5402.1599999999999</v>
       </c>
       <c r="L17" s="0">
-        <v>56.210000000000001</v>
+        <v>47.659999999999997</v>
       </c>
       <c r="M17" s="0">
-        <v>0.26000000000000001</v>
+        <v>0.17299999999999999</v>
       </c>
     </row>
     <row r="18">
@@ -886,40 +925,40 @@
         <v>17</v>
       </c>
       <c r="B18" s="0">
-        <v>2129212501</v>
+        <v>62764156494</v>
       </c>
       <c r="C18" s="0">
-        <v>2568132872</v>
+        <v>78357383553</v>
       </c>
       <c r="D18" s="0">
-        <v>193529</v>
+        <v>465057</v>
       </c>
       <c r="E18" s="0">
-        <v>76</v>
+        <v>142</v>
       </c>
       <c r="F18" s="0">
-        <v>69906</v>
+        <v>816022</v>
       </c>
       <c r="G18" s="0">
-        <v>5.2699999999999996</v>
+        <v>4.8399999999999999</v>
       </c>
       <c r="H18" s="0">
-        <v>8.4000000000000004</v>
+        <v>9.3000000000000007</v>
       </c>
       <c r="I18" s="0">
-        <v>82.909999999999997</v>
+        <v>80.099999999999994</v>
       </c>
       <c r="J18" s="0">
-        <v>483</v>
+        <v>680</v>
       </c>
       <c r="K18" s="0">
-        <v>1746</v>
+        <v>5121.3400000000001</v>
       </c>
       <c r="L18" s="0">
-        <v>22.98</v>
+        <v>36.25</v>
       </c>
       <c r="M18" s="0">
-        <v>0.080000000000000002</v>
+        <v>0.10199999999999999</v>
       </c>
     </row>
     <row r="19">
@@ -927,40 +966,40 @@
         <v>18</v>
       </c>
       <c r="B19" s="0">
-        <v>3423149052</v>
+        <v>146786899489</v>
       </c>
       <c r="C19" s="0">
-        <v>4089018798</v>
+        <v>177632550735</v>
       </c>
       <c r="D19" s="0">
-        <v>175947</v>
+        <v>580309</v>
       </c>
       <c r="E19" s="0">
-        <v>75</v>
+        <v>171</v>
       </c>
       <c r="F19" s="0">
-        <v>100082</v>
+        <v>1141186</v>
       </c>
       <c r="G19" s="0">
-        <v>4.3099999999999996</v>
+        <v>3.73</v>
       </c>
       <c r="H19" s="0">
-        <v>7.7400000000000002</v>
+        <v>9.25</v>
       </c>
       <c r="I19" s="0">
-        <v>83.719999999999999</v>
+        <v>82.640000000000001</v>
       </c>
       <c r="J19" s="0">
-        <v>541</v>
+        <v>915</v>
       </c>
       <c r="K19" s="0">
-        <v>2079</v>
+        <v>5496.3199999999997</v>
       </c>
       <c r="L19" s="0">
-        <v>27.550000000000001</v>
+        <v>32.289999999999999</v>
       </c>
       <c r="M19" s="0">
-        <v>0.089999999999999997</v>
+        <v>0.087999999999999995</v>
       </c>
     </row>
     <row r="20">
@@ -968,40 +1007,40 @@
         <v>19</v>
       </c>
       <c r="B20" s="0">
-        <v>1280029323</v>
+        <v>61324542034</v>
       </c>
       <c r="C20" s="0">
-        <v>1529120824</v>
+        <v>74285364300</v>
       </c>
       <c r="D20" s="0">
-        <v>72402</v>
+        <v>702595</v>
       </c>
       <c r="E20" s="0">
-        <v>50</v>
+        <v>173</v>
       </c>
       <c r="F20" s="0">
-        <v>104456</v>
+        <v>453332</v>
       </c>
       <c r="G20" s="0">
-        <v>4.9500000000000002</v>
+        <v>4.29</v>
       </c>
       <c r="H20" s="0">
-        <v>7.0599999999999996</v>
+        <v>10.73</v>
       </c>
       <c r="I20" s="0">
-        <v>83.709999999999994</v>
+        <v>82.549999999999997</v>
       </c>
       <c r="J20" s="0">
-        <v>293</v>
+        <v>949</v>
       </c>
       <c r="K20" s="0">
-        <v>2292</v>
+        <v>4625.0699999999997</v>
       </c>
       <c r="L20" s="0">
-        <v>45.850000000000001</v>
+        <v>26.780000000000001</v>
       </c>
       <c r="M20" s="0">
-        <v>0.22</v>
+        <v>0.070999999999999994</v>
       </c>
     </row>
     <row r="21">
@@ -1009,40 +1048,40 @@
         <v>20</v>
       </c>
       <c r="B21" s="0">
-        <v>4995828320</v>
+        <v>4406467602</v>
       </c>
       <c r="C21" s="0">
-        <v>6112355699</v>
+        <v>5376305619</v>
       </c>
       <c r="D21" s="0">
-        <v>142016</v>
+        <v>613034</v>
       </c>
       <c r="E21" s="0">
-        <v>72</v>
+        <v>178</v>
       </c>
       <c r="F21" s="0">
-        <v>197269</v>
+        <v>31870</v>
       </c>
       <c r="G21" s="0">
-        <v>4.5800000000000001</v>
+        <v>3.6299999999999999</v>
       </c>
       <c r="H21" s="0">
-        <v>7.5700000000000003</v>
+        <v>9.4299999999999997</v>
       </c>
       <c r="I21" s="0">
-        <v>81.730000000000004</v>
+        <v>81.959999999999994</v>
       </c>
       <c r="J21" s="0">
-        <v>428</v>
+        <v>945</v>
       </c>
       <c r="K21" s="0">
-        <v>2491</v>
+        <v>5259.8699999999999</v>
       </c>
       <c r="L21" s="0">
-        <v>34.439999999999998</v>
+        <v>29.469999999999999</v>
       </c>
       <c r="M21" s="0">
-        <v>0.13</v>
+        <v>0.081000000000000003</v>
       </c>
     </row>
     <row r="22">
@@ -1050,40 +1089,40 @@
         <v>21</v>
       </c>
       <c r="B22" s="0">
-        <v>8546315512</v>
+        <v>81928045437</v>
       </c>
       <c r="C22" s="0">
-        <v>11103075210</v>
+        <v>95290232546</v>
       </c>
       <c r="D22" s="0">
-        <v>136217</v>
+        <v>694738</v>
       </c>
       <c r="E22" s="0">
-        <v>74</v>
+        <v>179</v>
       </c>
       <c r="F22" s="0">
-        <v>308857</v>
+        <v>447358</v>
       </c>
       <c r="G22" s="0">
-        <v>3.79</v>
+        <v>3.2599999999999998</v>
       </c>
       <c r="H22" s="0">
-        <v>6.8899999999999997</v>
+        <v>9.9299999999999997</v>
       </c>
       <c r="I22" s="0">
-        <v>76.969999999999999</v>
+        <v>85.980000000000004</v>
       </c>
       <c r="J22" s="0">
-        <v>483</v>
+        <v>1190</v>
       </c>
       <c r="K22" s="0">
-        <v>1740</v>
+        <v>5592.6000000000004</v>
       </c>
       <c r="L22" s="0">
-        <v>23.41</v>
+        <v>31.25</v>
       </c>
       <c r="M22" s="0">
-        <v>0.089999999999999997</v>
+        <v>0.080000000000000002</v>
       </c>
     </row>
     <row r="23">
@@ -1091,40 +1130,40 @@
         <v>22</v>
       </c>
       <c r="B23" s="0">
-        <v>18132203156</v>
+        <v>31121347333</v>
       </c>
       <c r="C23" s="0">
-        <v>22136904081</v>
+        <v>36745876431</v>
       </c>
       <c r="D23" s="0">
-        <v>107055</v>
+        <v>867876</v>
       </c>
       <c r="E23" s="0">
-        <v>69</v>
+        <v>179</v>
       </c>
       <c r="F23" s="0">
-        <v>698026</v>
+        <v>136119</v>
       </c>
       <c r="G23" s="0">
-        <v>3.3799999999999999</v>
+        <v>3.21</v>
       </c>
       <c r="H23" s="0">
-        <v>5.5700000000000003</v>
+        <v>11.92</v>
       </c>
       <c r="I23" s="0">
-        <v>81.909999999999997</v>
+        <v>84.689999999999998</v>
       </c>
       <c r="J23" s="0">
-        <v>454</v>
+        <v>1512</v>
       </c>
       <c r="K23" s="0">
-        <v>1782</v>
+        <v>4467.9300000000003</v>
       </c>
       <c r="L23" s="0">
-        <v>25.710000000000001</v>
+        <v>25.02</v>
       </c>
       <c r="M23" s="0">
-        <v>0.089999999999999997</v>
+        <v>0.060999999999999999</v>
       </c>
     </row>
     <row r="24">
@@ -1132,40 +1171,573 @@
         <v>23</v>
       </c>
       <c r="B24" s="0">
+        <v>27270675985</v>
+      </c>
+      <c r="C24" s="0">
+        <v>31340900942</v>
+      </c>
+      <c r="D24" s="0">
+        <v>619141</v>
+      </c>
+      <c r="E24" s="0">
+        <v>188</v>
+      </c>
+      <c r="F24" s="0">
+        <v>148345</v>
+      </c>
+      <c r="G24" s="0">
+        <v>2.9300000000000002</v>
+      </c>
+      <c r="H24" s="0">
+        <v>8.6600000000000001</v>
+      </c>
+      <c r="I24" s="0">
+        <v>87.010000000000005</v>
+      </c>
+      <c r="J24" s="0">
+        <v>1152</v>
+      </c>
+      <c r="K24" s="0">
+        <v>6615.04</v>
+      </c>
+      <c r="L24" s="0">
+        <v>35.869999999999997</v>
+      </c>
+      <c r="M24" s="0">
+        <v>0.092999999999999999</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="0" t="s">
+        <v>24</v>
+      </c>
+      <c r="B25" s="0">
+        <v>10190157103</v>
+      </c>
+      <c r="C25" s="0">
+        <v>11723378333</v>
+      </c>
+      <c r="D25" s="0">
+        <v>873575</v>
+      </c>
+      <c r="E25" s="0">
+        <v>234</v>
+      </c>
+      <c r="F25" s="0">
+        <v>34773</v>
+      </c>
+      <c r="G25" s="0">
+        <v>2.5899999999999999</v>
+      </c>
+      <c r="H25" s="0">
+        <v>9.1500000000000004</v>
+      </c>
+      <c r="I25" s="0">
+        <v>86.920000000000002</v>
+      </c>
+      <c r="J25" s="0">
+        <v>1441</v>
+      </c>
+      <c r="K25" s="0">
+        <v>6976.7600000000002</v>
+      </c>
+      <c r="L25" s="0">
+        <v>29.82</v>
+      </c>
+      <c r="M25" s="0">
+        <v>0.072999999999999995</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="0" t="s">
+        <v>25</v>
+      </c>
+      <c r="B26" s="0">
+        <v>26611986471</v>
+      </c>
+      <c r="C26" s="0">
+        <v>30820516159</v>
+      </c>
+      <c r="D26" s="0">
+        <v>1038777</v>
+      </c>
+      <c r="E26" s="0">
+        <v>202</v>
+      </c>
+      <c r="F26" s="0">
+        <v>47236</v>
+      </c>
+      <c r="G26" s="0">
+        <v>1.5900000000000001</v>
+      </c>
+      <c r="H26" s="0">
+        <v>11.210000000000001</v>
+      </c>
+      <c r="I26" s="0">
+        <v>86.349999999999994</v>
+      </c>
+      <c r="J26" s="0">
+        <v>3261</v>
+      </c>
+      <c r="K26" s="0">
+        <v>8594.7800000000007</v>
+      </c>
+      <c r="L26" s="0">
+        <v>42.939999999999998</v>
+      </c>
+      <c r="M26" s="0">
+        <v>0.092999999999999999</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="0" t="s">
+        <v>26</v>
+      </c>
+      <c r="B27" s="0">
+        <v>14053041227</v>
+      </c>
+      <c r="C27" s="0">
+        <v>16727373751</v>
+      </c>
+      <c r="D27" s="0">
+        <v>1250177</v>
+      </c>
+      <c r="E27" s="0">
+        <v>234</v>
+      </c>
+      <c r="F27" s="0">
+        <v>19598</v>
+      </c>
+      <c r="G27" s="0">
+        <v>1.46</v>
+      </c>
+      <c r="H27" s="0">
+        <v>11.300000000000001</v>
+      </c>
+      <c r="I27" s="0">
+        <v>84.010000000000005</v>
+      </c>
+      <c r="J27" s="0">
+        <v>3643</v>
+      </c>
+      <c r="K27" s="0">
+        <v>9589.7600000000002</v>
+      </c>
+      <c r="L27" s="0">
+        <v>40.920000000000002</v>
+      </c>
+      <c r="M27" s="0">
+        <v>0.086999999999999994</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="0" t="s">
+        <v>27</v>
+      </c>
+      <c r="B28" s="0">
+        <v>16436017503</v>
+      </c>
+      <c r="C28" s="0">
+        <v>19694143083</v>
+      </c>
+      <c r="D28" s="0">
+        <v>1547065</v>
+      </c>
+      <c r="E28" s="0">
+        <v>263</v>
+      </c>
+      <c r="F28" s="0">
+        <v>21969</v>
+      </c>
+      <c r="G28" s="0">
+        <v>1.73</v>
+      </c>
+      <c r="H28" s="0">
+        <v>12.58</v>
+      </c>
+      <c r="I28" s="0">
+        <v>83.459999999999994</v>
+      </c>
+      <c r="J28" s="0">
+        <v>3442</v>
+      </c>
+      <c r="K28" s="0">
+        <v>9671.6100000000006</v>
+      </c>
+      <c r="L28" s="0">
+        <v>37.079999999999998</v>
+      </c>
+      <c r="M28" s="0">
+        <v>0.079000000000000001</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="0" t="s">
+        <v>28</v>
+      </c>
+      <c r="B29" s="0">
+        <v>17782793623</v>
+      </c>
+      <c r="C29" s="0">
+        <v>20859053979</v>
+      </c>
+      <c r="D29" s="0">
+        <v>1869091</v>
+      </c>
+      <c r="E29" s="0">
+        <v>282</v>
+      </c>
+      <c r="F29" s="0">
+        <v>17648</v>
+      </c>
+      <c r="G29" s="0">
+        <v>1.5800000000000001</v>
+      </c>
+      <c r="H29" s="0">
+        <v>13.720000000000001</v>
+      </c>
+      <c r="I29" s="0">
+        <v>85.25</v>
+      </c>
+      <c r="J29" s="0">
+        <v>4195</v>
+      </c>
+      <c r="K29" s="0">
+        <v>9703.9500000000007</v>
+      </c>
+      <c r="L29" s="0">
+        <v>34.439999999999998</v>
+      </c>
+      <c r="M29" s="0">
+        <v>0.070999999999999994</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="0" t="s">
+        <v>29</v>
+      </c>
+      <c r="B30" s="0">
+        <v>12759197716</v>
+      </c>
+      <c r="C30" s="0">
+        <v>15531091188</v>
+      </c>
+      <c r="D30" s="0">
+        <v>1891729</v>
+      </c>
+      <c r="E30" s="0">
+        <v>281</v>
+      </c>
+      <c r="F30" s="0">
+        <v>12014</v>
+      </c>
+      <c r="G30" s="0">
+        <v>1.46</v>
+      </c>
+      <c r="H30" s="0">
+        <v>13.91</v>
+      </c>
+      <c r="I30" s="0">
+        <v>82.150000000000006</v>
+      </c>
+      <c r="J30" s="0">
+        <v>4605</v>
+      </c>
+      <c r="K30" s="0">
+        <v>9330.6800000000003</v>
+      </c>
+      <c r="L30" s="0">
+        <v>33.240000000000002</v>
+      </c>
+      <c r="M30" s="0">
+        <v>0.069000000000000006</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="0" t="s">
+        <v>30</v>
+      </c>
+      <c r="B31" s="0">
+        <v>16804402831</v>
+      </c>
+      <c r="C31" s="0">
+        <v>20504977586</v>
+      </c>
+      <c r="D31" s="0">
+        <v>2034224</v>
+      </c>
+      <c r="E31" s="0">
+        <v>315</v>
+      </c>
+      <c r="F31" s="0">
+        <v>12085</v>
+      </c>
+      <c r="G31" s="0">
+        <v>1.2</v>
+      </c>
+      <c r="H31" s="0">
+        <v>12.91</v>
+      </c>
+      <c r="I31" s="0">
+        <v>81.950000000000003</v>
+      </c>
+      <c r="J31" s="0">
+        <v>5421</v>
+      </c>
+      <c r="K31" s="0">
+        <v>10282.190000000001</v>
+      </c>
+      <c r="L31" s="0">
+        <v>32.850000000000001</v>
+      </c>
+      <c r="M31" s="0">
+        <v>0.065000000000000002</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="0" t="s">
+        <v>31</v>
+      </c>
+      <c r="B32" s="0">
+        <v>20413854016</v>
+      </c>
+      <c r="C32" s="0">
+        <v>24045935719</v>
+      </c>
+      <c r="D32" s="0">
+        <v>1382745</v>
+      </c>
+      <c r="E32" s="0">
+        <v>236</v>
+      </c>
+      <c r="F32" s="0">
+        <v>24916</v>
+      </c>
+      <c r="G32" s="0">
+        <v>1.4299999999999999</v>
+      </c>
+      <c r="H32" s="0">
+        <v>11.779999999999999</v>
+      </c>
+      <c r="I32" s="0">
+        <v>84.900000000000006</v>
+      </c>
+      <c r="J32" s="0">
+        <v>4091</v>
+      </c>
+      <c r="K32" s="0">
+        <v>11826.639999999999</v>
+      </c>
+      <c r="L32" s="0">
+        <v>50.130000000000003</v>
+      </c>
+      <c r="M32" s="0">
+        <v>0.10100000000000001</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="0" t="s">
+        <v>32</v>
+      </c>
+      <c r="B33" s="0">
+        <v>32165933845</v>
+      </c>
+      <c r="C33" s="0">
+        <v>39193909732</v>
+      </c>
+      <c r="D33" s="0">
+        <v>1789676</v>
+      </c>
+      <c r="E33" s="0">
+        <v>268</v>
+      </c>
+      <c r="F33" s="0">
+        <v>28722</v>
+      </c>
+      <c r="G33" s="0">
+        <v>1.3100000000000001</v>
+      </c>
+      <c r="H33" s="0">
+        <v>13.289999999999999</v>
+      </c>
+      <c r="I33" s="0">
+        <v>82.069999999999993</v>
+      </c>
+      <c r="J33" s="0">
+        <v>5125</v>
+      </c>
+      <c r="K33" s="0">
+        <v>11055.360000000001</v>
+      </c>
+      <c r="L33" s="0">
+        <v>41.490000000000002</v>
+      </c>
+      <c r="M33" s="0">
+        <v>0.082000000000000003</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="0" t="s">
+        <v>33</v>
+      </c>
+      <c r="B34" s="0">
+        <v>13602227910</v>
+      </c>
+      <c r="C34" s="0">
+        <v>15899831778</v>
+      </c>
+      <c r="D34" s="0">
+        <v>2094839</v>
+      </c>
+      <c r="E34" s="0">
+        <v>318</v>
+      </c>
+      <c r="F34" s="0">
+        <v>11785</v>
+      </c>
+      <c r="G34" s="0">
+        <v>1.55</v>
+      </c>
+      <c r="H34" s="0">
+        <v>13.24</v>
+      </c>
+      <c r="I34" s="0">
+        <v>85.549999999999997</v>
+      </c>
+      <c r="J34" s="0">
+        <v>4243</v>
+      </c>
+      <c r="K34" s="0">
+        <v>9695.5699999999997</v>
+      </c>
+      <c r="L34" s="0">
+        <v>30.489999999999998</v>
+      </c>
+      <c r="M34" s="0">
+        <v>0.060999999999999999</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="0" t="s">
+        <v>34</v>
+      </c>
+      <c r="B35" s="0">
+        <v>55046861752</v>
+      </c>
+      <c r="C35" s="0">
+        <v>67222585980</v>
+      </c>
+      <c r="D35" s="0">
+        <v>1521906</v>
+      </c>
+      <c r="E35" s="0">
+        <v>296</v>
+      </c>
+      <c r="F35" s="0">
+        <v>64789</v>
+      </c>
+      <c r="G35" s="0">
+        <v>1.47</v>
+      </c>
+      <c r="H35" s="0">
+        <v>10.98</v>
+      </c>
+      <c r="I35" s="0">
+        <v>81.890000000000001</v>
+      </c>
+      <c r="J35" s="0">
+        <v>3620</v>
+      </c>
+      <c r="K35" s="0">
+        <v>12821.780000000001</v>
+      </c>
+      <c r="L35" s="0">
+        <v>44.579999999999998</v>
+      </c>
+      <c r="M35" s="0">
+        <v>0.092999999999999999</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="0" t="s">
+        <v>35</v>
+      </c>
+      <c r="B36" s="0">
+        <v>24814388925</v>
+      </c>
+      <c r="C36" s="0">
+        <v>31020857567</v>
+      </c>
+      <c r="D36" s="0">
+        <v>2027507</v>
+      </c>
+      <c r="E36" s="0">
+        <v>329</v>
+      </c>
+      <c r="F36" s="0">
+        <v>19311</v>
+      </c>
+      <c r="G36" s="0">
+        <v>1.26</v>
+      </c>
+      <c r="H36" s="0">
+        <v>12.32</v>
+      </c>
+      <c r="I36" s="0">
+        <v>79.989999999999995</v>
+      </c>
+      <c r="J36" s="0">
+        <v>4881</v>
+      </c>
+      <c r="K36" s="0">
+        <v>14456.959999999999</v>
+      </c>
+      <c r="L36" s="0">
+        <v>43.969999999999999</v>
+      </c>
+      <c r="M36" s="0">
+        <v>0.087999999999999995</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="0" t="s">
+        <v>36</v>
+      </c>
+      <c r="B37" s="0">
         <v>1075495737674</v>
       </c>
-      <c r="C24" s="0">
+      <c r="C37" s="0">
         <v>1290645368239</v>
       </c>
-      <c r="D24" s="0">
+      <c r="D37" s="0">
         <v>556946</v>
       </c>
-      <c r="E24" s="0">
+      <c r="E37" s="0">
         <v>144</v>
       </c>
-      <c r="F24" s="0">
+      <c r="F37" s="0">
         <v>8038577</v>
       </c>
-      <c r="G24" s="0">
+      <c r="G37" s="0">
         <v>3.4700000000000002</v>
       </c>
-      <c r="H24" s="0">
+      <c r="H37" s="0">
         <v>8.8200000000000003</v>
       </c>
-      <c r="I24" s="0">
+      <c r="I37" s="0">
         <v>83.329999999999998</v>
       </c>
-      <c r="J24" s="0">
+      <c r="J37" s="0">
         <v>937</v>
       </c>
-      <c r="K24" s="0">
-        <v>5469</v>
-      </c>
-      <c r="L24" s="0">
+      <c r="K37" s="0">
+        <v>5468.8299999999999</v>
+      </c>
+      <c r="L37" s="0">
         <v>33.640000000000001</v>
       </c>
-      <c r="M24" s="0">
-        <v>0.089999999999999997</v>
+      <c r="M37" s="0">
+        <v>0.086999999999999994</v>
       </c>
     </row>
   </sheetData>

--- a/Output Data Tables/APAT Outputs/Aggregated Tables/2023/Aircraft_Cumulative_Statistics_2023.xlsx
+++ b/Output Data Tables/APAT Outputs/Aggregated Tables/2023/Aircraft_Cumulative_Statistics_2023.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="49" uniqueCount="49">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="52" uniqueCount="52">
   <si>
     <t>Row</t>
   </si>
@@ -30,7 +30,10 @@
     <t>E175</t>
   </si>
   <si>
-    <t>CRJ-500</t>
+    <t>Q400</t>
+  </si>
+  <si>
+    <t>CRJ-550</t>
   </si>
   <si>
     <t>CRJ-700</t>
@@ -63,7 +66,13 @@
     <t>A321NEO</t>
   </si>
   <si>
+    <t>MD-80</t>
+  </si>
+  <si>
     <t>B717-200</t>
+  </si>
+  <si>
+    <t>B737-400</t>
   </si>
   <si>
     <t>B737-700</t>
@@ -205,7 +214,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:M37"/>
+  <dimension ref="A1:M40"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="11.140625" customWidth="true"/>
@@ -228,40 +237,40 @@
         <v>0</v>
       </c>
       <c r="B1" s="0" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="C1" s="0" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="D1" s="0" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="E1" s="0" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="F1" s="0" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="G1" s="0" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="H1" s="0" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="I1" s="0" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="J1" s="0" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="K1" s="0" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="L1" s="0" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="M1" s="0" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
     </row>
     <row r="2">
@@ -433,40 +442,40 @@
         <v>5</v>
       </c>
       <c r="B6" s="0">
-        <v>606963891</v>
+        <v>5360970</v>
       </c>
       <c r="C6" s="0">
-        <v>735124450</v>
+        <v>6834452</v>
       </c>
       <c r="D6" s="0">
-        <v>30066</v>
+        <v>40203</v>
       </c>
       <c r="E6" s="0">
-        <v>50</v>
+        <v>76</v>
       </c>
       <c r="F6" s="0">
-        <v>45438</v>
+        <v>509</v>
       </c>
       <c r="G6" s="0">
-        <v>1.8600000000000001</v>
+        <v>2.9900000000000002</v>
       </c>
       <c r="H6" s="0">
-        <v>2.8100000000000001</v>
+        <v>2.9399999999999999</v>
       </c>
       <c r="I6" s="0">
-        <v>82.569999999999993</v>
+        <v>78.439999999999998</v>
       </c>
       <c r="J6" s="0">
-        <v>324</v>
+        <v>177</v>
       </c>
       <c r="K6" s="0">
-        <v>2810.73</v>
+        <v>27362</v>
       </c>
       <c r="L6" s="0">
-        <v>56.210000000000001</v>
+        <v>360.02999999999997</v>
       </c>
       <c r="M6" s="0">
-        <v>0.26200000000000001</v>
+        <v>2.0019999999999998</v>
       </c>
     </row>
     <row r="7">
@@ -474,40 +483,40 @@
         <v>6</v>
       </c>
       <c r="B7" s="0">
-        <v>4811058348</v>
+        <v>606963891</v>
       </c>
       <c r="C7" s="0">
-        <v>6121509112</v>
+        <v>735124450</v>
       </c>
       <c r="D7" s="0">
-        <v>89222</v>
+        <v>30066</v>
       </c>
       <c r="E7" s="0">
-        <v>66</v>
+        <v>50</v>
       </c>
       <c r="F7" s="0">
-        <v>216349</v>
+        <v>45438</v>
       </c>
       <c r="G7" s="0">
-        <v>3.1499999999999999</v>
+        <v>1.8600000000000001</v>
       </c>
       <c r="H7" s="0">
-        <v>5.0800000000000001</v>
+        <v>2.8100000000000001</v>
       </c>
       <c r="I7" s="0">
-        <v>78.590000000000003</v>
+        <v>82.569999999999993</v>
       </c>
       <c r="J7" s="0">
-        <v>428</v>
+        <v>324</v>
       </c>
       <c r="K7" s="0">
-        <v>2567.5900000000001</v>
+        <v>2810.73</v>
       </c>
       <c r="L7" s="0">
-        <v>38.890000000000001</v>
+        <v>56.210000000000001</v>
       </c>
       <c r="M7" s="0">
-        <v>0.14599999999999999</v>
+        <v>0.26200000000000001</v>
       </c>
     </row>
     <row r="8">
@@ -515,40 +524,40 @@
         <v>7</v>
       </c>
       <c r="B8" s="0">
-        <v>3328424207</v>
+        <v>4811058348</v>
       </c>
       <c r="C8" s="0">
-        <v>4120279832</v>
+        <v>6121509112</v>
       </c>
       <c r="D8" s="0">
-        <v>236119</v>
+        <v>89222</v>
       </c>
       <c r="E8" s="0">
-        <v>101</v>
+        <v>66</v>
       </c>
       <c r="F8" s="0">
-        <v>81316</v>
+        <v>216349</v>
       </c>
       <c r="G8" s="0">
-        <v>4.6600000000000001</v>
+        <v>3.1499999999999999</v>
       </c>
       <c r="H8" s="0">
-        <v>8.3399999999999999</v>
+        <v>5.0800000000000001</v>
       </c>
       <c r="I8" s="0">
-        <v>80.780000000000001</v>
+        <v>78.590000000000003</v>
       </c>
       <c r="J8" s="0">
-        <v>503</v>
+        <v>428</v>
       </c>
       <c r="K8" s="0">
-        <v>5513.1599999999999</v>
+        <v>2567.5900000000001</v>
       </c>
       <c r="L8" s="0">
-        <v>54.789999999999999</v>
+        <v>38.890000000000001</v>
       </c>
       <c r="M8" s="0">
-        <v>0.19500000000000001</v>
+        <v>0.14599999999999999</v>
       </c>
     </row>
     <row r="9">
@@ -556,40 +565,40 @@
         <v>8</v>
       </c>
       <c r="B9" s="0">
-        <v>10990857295</v>
+        <v>3328424207</v>
       </c>
       <c r="C9" s="0">
-        <v>13435631377</v>
+        <v>4120279832</v>
       </c>
       <c r="D9" s="0">
-        <v>145156</v>
+        <v>236119</v>
       </c>
       <c r="E9" s="0">
-        <v>75</v>
+        <v>101</v>
       </c>
       <c r="F9" s="0">
-        <v>415846</v>
+        <v>81316</v>
       </c>
       <c r="G9" s="0">
-        <v>4.4900000000000002</v>
+        <v>4.6600000000000001</v>
       </c>
       <c r="H9" s="0">
-        <v>7.2699999999999996</v>
+        <v>8.3399999999999999</v>
       </c>
       <c r="I9" s="0">
-        <v>81.799999999999997</v>
+        <v>80.780000000000001</v>
       </c>
       <c r="J9" s="0">
-        <v>429</v>
+        <v>503</v>
       </c>
       <c r="K9" s="0">
-        <v>2096.96</v>
+        <v>5513.1599999999999</v>
       </c>
       <c r="L9" s="0">
-        <v>27.82</v>
+        <v>54.789999999999999</v>
       </c>
       <c r="M9" s="0">
-        <v>0.105</v>
+        <v>0.19500000000000001</v>
       </c>
     </row>
     <row r="10">
@@ -597,40 +606,40 @@
         <v>9</v>
       </c>
       <c r="B10" s="0">
-        <v>5042223818</v>
+        <v>10990857295</v>
       </c>
       <c r="C10" s="0">
-        <v>5940796394</v>
+        <v>13435631377</v>
       </c>
       <c r="D10" s="0">
-        <v>366716</v>
+        <v>145156</v>
       </c>
       <c r="E10" s="0">
-        <v>109</v>
+        <v>75</v>
       </c>
       <c r="F10" s="0">
-        <v>58208</v>
+        <v>415846</v>
       </c>
       <c r="G10" s="0">
-        <v>3.5899999999999999</v>
+        <v>4.4900000000000002</v>
       </c>
       <c r="H10" s="0">
-        <v>9.4800000000000004</v>
+        <v>7.2699999999999996</v>
       </c>
       <c r="I10" s="0">
-        <v>84.870000000000005</v>
+        <v>81.799999999999997</v>
       </c>
       <c r="J10" s="0">
-        <v>937</v>
+        <v>429</v>
       </c>
       <c r="K10" s="0">
-        <v>4983.1599999999999</v>
+        <v>2096.96</v>
       </c>
       <c r="L10" s="0">
-        <v>45.729999999999997</v>
+        <v>27.82</v>
       </c>
       <c r="M10" s="0">
-        <v>0.129</v>
+        <v>0.105</v>
       </c>
     </row>
     <row r="11">
@@ -638,40 +647,40 @@
         <v>10</v>
       </c>
       <c r="B11" s="0">
-        <v>7165334582</v>
+        <v>5042223818</v>
       </c>
       <c r="C11" s="0">
-        <v>8777447933</v>
+        <v>5940796394</v>
       </c>
       <c r="D11" s="0">
-        <v>707288</v>
+        <v>366716</v>
       </c>
       <c r="E11" s="0">
-        <v>134</v>
+        <v>109</v>
       </c>
       <c r="F11" s="0">
-        <v>58569</v>
+        <v>58208</v>
       </c>
       <c r="G11" s="0">
-        <v>4.7199999999999998</v>
+        <v>3.5899999999999999</v>
       </c>
       <c r="H11" s="0">
-        <v>14</v>
+        <v>9.4800000000000004</v>
       </c>
       <c r="I11" s="0">
-        <v>81.629999999999995</v>
+        <v>84.870000000000005</v>
       </c>
       <c r="J11" s="0">
-        <v>1114</v>
+        <v>937</v>
       </c>
       <c r="K11" s="0">
-        <v>3835.1799999999998</v>
+        <v>4983.1599999999999</v>
       </c>
       <c r="L11" s="0">
-        <v>28.5</v>
+        <v>45.729999999999997</v>
       </c>
       <c r="M11" s="0">
-        <v>0.075999999999999998</v>
+        <v>0.129</v>
       </c>
     </row>
     <row r="12">
@@ -679,40 +688,40 @@
         <v>11</v>
       </c>
       <c r="B12" s="0">
-        <v>38332240832</v>
+        <v>7165334582</v>
       </c>
       <c r="C12" s="0">
-        <v>45966398192</v>
+        <v>8777447933</v>
       </c>
       <c r="D12" s="0">
-        <v>385592</v>
+        <v>707288</v>
       </c>
       <c r="E12" s="0">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="F12" s="0">
-        <v>446753</v>
+        <v>58569</v>
       </c>
       <c r="G12" s="0">
-        <v>3.75</v>
+        <v>4.7199999999999998</v>
       </c>
       <c r="H12" s="0">
-        <v>8.4499999999999993</v>
+        <v>14</v>
       </c>
       <c r="I12" s="0">
-        <v>83.390000000000001</v>
+        <v>81.629999999999995</v>
       </c>
       <c r="J12" s="0">
-        <v>780</v>
+        <v>1114</v>
       </c>
       <c r="K12" s="0">
-        <v>5238.4399999999996</v>
+        <v>3835.1799999999998</v>
       </c>
       <c r="L12" s="0">
-        <v>39.780000000000001</v>
+        <v>28.5</v>
       </c>
       <c r="M12" s="0">
-        <v>0.115</v>
+        <v>0.075999999999999998</v>
       </c>
     </row>
     <row r="13">
@@ -720,40 +729,40 @@
         <v>12</v>
       </c>
       <c r="B13" s="0">
-        <v>83263671726</v>
+        <v>38332240832</v>
       </c>
       <c r="C13" s="0">
-        <v>100304254392</v>
+        <v>45966398192</v>
       </c>
       <c r="D13" s="0">
-        <v>553311</v>
+        <v>385592</v>
       </c>
       <c r="E13" s="0">
-        <v>164</v>
+        <v>132</v>
       </c>
       <c r="F13" s="0">
-        <v>643900</v>
+        <v>446753</v>
       </c>
       <c r="G13" s="0">
-        <v>3.5499999999999998</v>
+        <v>3.75</v>
       </c>
       <c r="H13" s="0">
-        <v>9.1699999999999999</v>
+        <v>8.4499999999999993</v>
       </c>
       <c r="I13" s="0">
-        <v>83.010000000000005</v>
+        <v>83.390000000000001</v>
       </c>
       <c r="J13" s="0">
-        <v>947</v>
+        <v>780</v>
       </c>
       <c r="K13" s="0">
-        <v>5526.6899999999996</v>
+        <v>5238.4399999999996</v>
       </c>
       <c r="L13" s="0">
-        <v>33.659999999999997</v>
+        <v>39.780000000000001</v>
       </c>
       <c r="M13" s="0">
-        <v>0.091999999999999998</v>
+        <v>0.115</v>
       </c>
     </row>
     <row r="14">
@@ -761,40 +770,40 @@
         <v>13</v>
       </c>
       <c r="B14" s="0">
-        <v>37390349543</v>
+        <v>83263671726</v>
       </c>
       <c r="C14" s="0">
-        <v>45247127300</v>
+        <v>100304254392</v>
       </c>
       <c r="D14" s="0">
-        <v>764310</v>
+        <v>553311</v>
       </c>
       <c r="E14" s="0">
-        <v>184</v>
+        <v>164</v>
       </c>
       <c r="F14" s="0">
-        <v>236739</v>
+        <v>643900</v>
       </c>
       <c r="G14" s="0">
-        <v>4</v>
+        <v>3.5499999999999998</v>
       </c>
       <c r="H14" s="0">
-        <v>11.19</v>
+        <v>9.1699999999999999</v>
       </c>
       <c r="I14" s="0">
-        <v>82.640000000000001</v>
+        <v>83.010000000000005</v>
       </c>
       <c r="J14" s="0">
-        <v>1038</v>
+        <v>947</v>
       </c>
       <c r="K14" s="0">
-        <v>4660.0799999999999</v>
+        <v>5526.6899999999996</v>
       </c>
       <c r="L14" s="0">
-        <v>25.309999999999999</v>
+        <v>33.659999999999997</v>
       </c>
       <c r="M14" s="0">
-        <v>0.068000000000000005</v>
+        <v>0.091999999999999998</v>
       </c>
     </row>
     <row r="15">
@@ -802,40 +811,40 @@
         <v>14</v>
       </c>
       <c r="B15" s="0">
-        <v>112260940495</v>
+        <v>37390349543</v>
       </c>
       <c r="C15" s="0">
-        <v>132270457295</v>
+        <v>45247127300</v>
       </c>
       <c r="D15" s="0">
-        <v>796666</v>
+        <v>764310</v>
       </c>
       <c r="E15" s="0">
-        <v>192</v>
+        <v>184</v>
       </c>
       <c r="F15" s="0">
-        <v>609729</v>
+        <v>236739</v>
       </c>
       <c r="G15" s="0">
-        <v>3.6699999999999999</v>
+        <v>4</v>
       </c>
       <c r="H15" s="0">
-        <v>11.06</v>
+        <v>11.19</v>
       </c>
       <c r="I15" s="0">
-        <v>84.870000000000005</v>
+        <v>82.640000000000001</v>
       </c>
       <c r="J15" s="0">
-        <v>1156</v>
+        <v>1038</v>
       </c>
       <c r="K15" s="0">
-        <v>6012.0600000000004</v>
+        <v>4660.0799999999999</v>
       </c>
       <c r="L15" s="0">
-        <v>31.879999999999999</v>
+        <v>25.309999999999999</v>
       </c>
       <c r="M15" s="0">
-        <v>0.083000000000000004</v>
+        <v>0.068000000000000005</v>
       </c>
     </row>
     <row r="16">
@@ -843,40 +852,40 @@
         <v>15</v>
       </c>
       <c r="B16" s="0">
-        <v>52356590976</v>
+        <v>112260940495</v>
       </c>
       <c r="C16" s="0">
-        <v>62104598448</v>
+        <v>132270457295</v>
       </c>
       <c r="D16" s="0">
-        <v>976795</v>
+        <v>796666</v>
       </c>
       <c r="E16" s="0">
-        <v>200</v>
+        <v>192</v>
       </c>
       <c r="F16" s="0">
-        <v>175525</v>
+        <v>609729</v>
       </c>
       <c r="G16" s="0">
-        <v>2.7599999999999998</v>
+        <v>3.6699999999999999</v>
       </c>
       <c r="H16" s="0">
-        <v>11.82</v>
+        <v>11.06</v>
       </c>
       <c r="I16" s="0">
-        <v>84.299999999999997</v>
+        <v>84.870000000000005</v>
       </c>
       <c r="J16" s="0">
-        <v>1808</v>
+        <v>1156</v>
       </c>
       <c r="K16" s="0">
-        <v>6199.8599999999997</v>
+        <v>6012.0600000000004</v>
       </c>
       <c r="L16" s="0">
-        <v>31.57</v>
+        <v>31.879999999999999</v>
       </c>
       <c r="M16" s="0">
-        <v>0.074999999999999997</v>
+        <v>0.083000000000000004</v>
       </c>
     </row>
     <row r="17">
@@ -884,40 +893,40 @@
         <v>16</v>
       </c>
       <c r="B17" s="0">
-        <v>6343882022</v>
+        <v>52356590976</v>
       </c>
       <c r="C17" s="0">
-        <v>7530081594</v>
+        <v>62104598448</v>
       </c>
       <c r="D17" s="0">
-        <v>232123</v>
+        <v>976795</v>
       </c>
       <c r="E17" s="0">
-        <v>116</v>
+        <v>200</v>
       </c>
       <c r="F17" s="0">
-        <v>186904</v>
+        <v>175525</v>
       </c>
       <c r="G17" s="0">
-        <v>5.7599999999999998</v>
+        <v>2.7599999999999998</v>
       </c>
       <c r="H17" s="0">
-        <v>7.4400000000000004</v>
+        <v>11.82</v>
       </c>
       <c r="I17" s="0">
-        <v>84.25</v>
+        <v>84.299999999999997</v>
       </c>
       <c r="J17" s="0">
-        <v>359</v>
+        <v>1808</v>
       </c>
       <c r="K17" s="0">
-        <v>5402.1599999999999</v>
+        <v>6199.8599999999997</v>
       </c>
       <c r="L17" s="0">
-        <v>47.659999999999997</v>
+        <v>31.57</v>
       </c>
       <c r="M17" s="0">
-        <v>0.17299999999999999</v>
+        <v>0.074999999999999997</v>
       </c>
     </row>
     <row r="18">
@@ -925,40 +934,40 @@
         <v>17</v>
       </c>
       <c r="B18" s="0">
-        <v>62764156494</v>
+        <v>532585</v>
       </c>
       <c r="C18" s="0">
-        <v>78357383553</v>
+        <v>614200</v>
       </c>
       <c r="D18" s="0">
-        <v>465057</v>
+        <v>0</v>
       </c>
       <c r="E18" s="0">
-        <v>142</v>
+        <v>166</v>
       </c>
       <c r="F18" s="0">
-        <v>816022</v>
+        <v>4</v>
       </c>
       <c r="G18" s="0">
-        <v>4.8399999999999999</v>
+        <v>0</v>
       </c>
       <c r="H18" s="0">
-        <v>9.3000000000000007</v>
+        <v>0</v>
       </c>
       <c r="I18" s="0">
-        <v>80.099999999999994</v>
+        <v>86.709999999999994</v>
       </c>
       <c r="J18" s="0">
-        <v>680</v>
+        <v>925</v>
       </c>
       <c r="K18" s="0">
-        <v>5121.3400000000001</v>
+        <v>0</v>
       </c>
       <c r="L18" s="0">
-        <v>36.25</v>
+        <v>0</v>
       </c>
       <c r="M18" s="0">
-        <v>0.10199999999999999</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -966,40 +975,40 @@
         <v>18</v>
       </c>
       <c r="B19" s="0">
-        <v>146786899489</v>
+        <v>6343882022</v>
       </c>
       <c r="C19" s="0">
-        <v>177632550735</v>
+        <v>7530081594</v>
       </c>
       <c r="D19" s="0">
-        <v>580309</v>
+        <v>232123</v>
       </c>
       <c r="E19" s="0">
-        <v>171</v>
+        <v>116</v>
       </c>
       <c r="F19" s="0">
-        <v>1141186</v>
+        <v>186904</v>
       </c>
       <c r="G19" s="0">
-        <v>3.73</v>
+        <v>5.7599999999999998</v>
       </c>
       <c r="H19" s="0">
-        <v>9.25</v>
+        <v>7.4400000000000004</v>
       </c>
       <c r="I19" s="0">
-        <v>82.640000000000001</v>
+        <v>84.25</v>
       </c>
       <c r="J19" s="0">
-        <v>915</v>
+        <v>359</v>
       </c>
       <c r="K19" s="0">
-        <v>5496.3199999999997</v>
+        <v>5402.1599999999999</v>
       </c>
       <c r="L19" s="0">
-        <v>32.289999999999999</v>
+        <v>47.659999999999997</v>
       </c>
       <c r="M19" s="0">
-        <v>0.087999999999999995</v>
+        <v>0.17299999999999999</v>
       </c>
     </row>
     <row r="20">
@@ -1007,40 +1016,40 @@
         <v>19</v>
       </c>
       <c r="B20" s="0">
-        <v>61324542034</v>
+        <v>2233015</v>
       </c>
       <c r="C20" s="0">
-        <v>74285364300</v>
+        <v>2829711</v>
       </c>
       <c r="D20" s="0">
-        <v>702595</v>
+        <v>0</v>
       </c>
       <c r="E20" s="0">
-        <v>173</v>
+        <v>127</v>
       </c>
       <c r="F20" s="0">
-        <v>453332</v>
+        <v>23</v>
       </c>
       <c r="G20" s="0">
-        <v>4.29</v>
+        <v>0</v>
       </c>
       <c r="H20" s="0">
-        <v>10.73</v>
+        <v>0</v>
       </c>
       <c r="I20" s="0">
-        <v>82.549999999999997</v>
+        <v>78.909999999999997</v>
       </c>
       <c r="J20" s="0">
-        <v>949</v>
+        <v>948</v>
       </c>
       <c r="K20" s="0">
-        <v>4625.0699999999997</v>
+        <v>194001.29000000001</v>
       </c>
       <c r="L20" s="0">
-        <v>26.780000000000001</v>
+        <v>1504.79</v>
       </c>
       <c r="M20" s="0">
-        <v>0.070999999999999994</v>
+        <v>3.903</v>
       </c>
     </row>
     <row r="21">
@@ -1048,40 +1057,40 @@
         <v>20</v>
       </c>
       <c r="B21" s="0">
-        <v>4406467602</v>
+        <v>63600056469</v>
       </c>
       <c r="C21" s="0">
-        <v>5376305619</v>
+        <v>79362523702</v>
       </c>
       <c r="D21" s="0">
-        <v>613034</v>
+        <v>471022</v>
       </c>
       <c r="E21" s="0">
-        <v>178</v>
+        <v>142</v>
       </c>
       <c r="F21" s="0">
-        <v>31870</v>
+        <v>824931</v>
       </c>
       <c r="G21" s="0">
-        <v>3.6299999999999999</v>
+        <v>4.9000000000000004</v>
       </c>
       <c r="H21" s="0">
-        <v>9.4299999999999997</v>
+        <v>9.4100000000000001</v>
       </c>
       <c r="I21" s="0">
-        <v>81.959999999999994</v>
+        <v>80.140000000000001</v>
       </c>
       <c r="J21" s="0">
-        <v>945</v>
+        <v>680</v>
       </c>
       <c r="K21" s="0">
-        <v>5259.8699999999999</v>
+        <v>5058.04</v>
       </c>
       <c r="L21" s="0">
-        <v>29.469999999999999</v>
+        <v>35.780000000000001</v>
       </c>
       <c r="M21" s="0">
-        <v>0.081000000000000003</v>
+        <v>0.10100000000000001</v>
       </c>
     </row>
     <row r="22">
@@ -1089,40 +1098,40 @@
         <v>21</v>
       </c>
       <c r="B22" s="0">
-        <v>81928045437</v>
+        <v>147810541920</v>
       </c>
       <c r="C22" s="0">
-        <v>95290232546</v>
+        <v>179017007109</v>
       </c>
       <c r="D22" s="0">
-        <v>694738</v>
+        <v>584832</v>
       </c>
       <c r="E22" s="0">
-        <v>179</v>
+        <v>171</v>
       </c>
       <c r="F22" s="0">
-        <v>447358</v>
+        <v>1150101</v>
       </c>
       <c r="G22" s="0">
-        <v>3.2599999999999998</v>
+        <v>3.7599999999999998</v>
       </c>
       <c r="H22" s="0">
-        <v>9.9299999999999997</v>
+        <v>9.3200000000000003</v>
       </c>
       <c r="I22" s="0">
-        <v>85.980000000000004</v>
+        <v>82.569999999999993</v>
       </c>
       <c r="J22" s="0">
-        <v>1190</v>
+        <v>914</v>
       </c>
       <c r="K22" s="0">
-        <v>5592.6000000000004</v>
+        <v>5456.1700000000001</v>
       </c>
       <c r="L22" s="0">
-        <v>31.25</v>
+        <v>32.030000000000001</v>
       </c>
       <c r="M22" s="0">
-        <v>0.080000000000000002</v>
+        <v>0.086999999999999994</v>
       </c>
     </row>
     <row r="23">
@@ -1130,40 +1139,40 @@
         <v>22</v>
       </c>
       <c r="B23" s="0">
-        <v>31121347333</v>
+        <v>61324542034</v>
       </c>
       <c r="C23" s="0">
-        <v>36745876431</v>
+        <v>74285364300</v>
       </c>
       <c r="D23" s="0">
-        <v>867876</v>
+        <v>702595</v>
       </c>
       <c r="E23" s="0">
-        <v>179</v>
+        <v>173</v>
       </c>
       <c r="F23" s="0">
-        <v>136119</v>
+        <v>453332</v>
       </c>
       <c r="G23" s="0">
-        <v>3.21</v>
+        <v>4.29</v>
       </c>
       <c r="H23" s="0">
-        <v>11.92</v>
+        <v>10.73</v>
       </c>
       <c r="I23" s="0">
-        <v>84.689999999999998</v>
+        <v>82.549999999999997</v>
       </c>
       <c r="J23" s="0">
-        <v>1512</v>
+        <v>949</v>
       </c>
       <c r="K23" s="0">
-        <v>4467.9300000000003</v>
+        <v>4625.0699999999997</v>
       </c>
       <c r="L23" s="0">
-        <v>25.02</v>
+        <v>26.780000000000001</v>
       </c>
       <c r="M23" s="0">
-        <v>0.060999999999999999</v>
+        <v>0.070999999999999994</v>
       </c>
     </row>
     <row r="24">
@@ -1171,40 +1180,40 @@
         <v>23</v>
       </c>
       <c r="B24" s="0">
-        <v>27270675985</v>
+        <v>4406467602</v>
       </c>
       <c r="C24" s="0">
-        <v>31340900942</v>
+        <v>5376305619</v>
       </c>
       <c r="D24" s="0">
-        <v>619141</v>
+        <v>613034</v>
       </c>
       <c r="E24" s="0">
-        <v>188</v>
+        <v>178</v>
       </c>
       <c r="F24" s="0">
-        <v>148345</v>
+        <v>31870</v>
       </c>
       <c r="G24" s="0">
-        <v>2.9300000000000002</v>
+        <v>3.6299999999999999</v>
       </c>
       <c r="H24" s="0">
-        <v>8.6600000000000001</v>
+        <v>9.4299999999999997</v>
       </c>
       <c r="I24" s="0">
-        <v>87.010000000000005</v>
+        <v>81.959999999999994</v>
       </c>
       <c r="J24" s="0">
-        <v>1152</v>
+        <v>945</v>
       </c>
       <c r="K24" s="0">
-        <v>6615.04</v>
+        <v>5259.8699999999999</v>
       </c>
       <c r="L24" s="0">
-        <v>35.869999999999997</v>
+        <v>29.469999999999999</v>
       </c>
       <c r="M24" s="0">
-        <v>0.092999999999999999</v>
+        <v>0.081000000000000003</v>
       </c>
     </row>
     <row r="25">
@@ -1212,40 +1221,40 @@
         <v>24</v>
       </c>
       <c r="B25" s="0">
-        <v>10190157103</v>
+        <v>81928045437</v>
       </c>
       <c r="C25" s="0">
-        <v>11723378333</v>
+        <v>95290232546</v>
       </c>
       <c r="D25" s="0">
-        <v>873575</v>
+        <v>694738</v>
       </c>
       <c r="E25" s="0">
-        <v>234</v>
+        <v>179</v>
       </c>
       <c r="F25" s="0">
-        <v>34773</v>
+        <v>447358</v>
       </c>
       <c r="G25" s="0">
-        <v>2.5899999999999999</v>
+        <v>3.2599999999999998</v>
       </c>
       <c r="H25" s="0">
-        <v>9.1500000000000004</v>
+        <v>9.9299999999999997</v>
       </c>
       <c r="I25" s="0">
-        <v>86.920000000000002</v>
+        <v>85.980000000000004</v>
       </c>
       <c r="J25" s="0">
-        <v>1441</v>
+        <v>1190</v>
       </c>
       <c r="K25" s="0">
-        <v>6976.7600000000002</v>
+        <v>5592.6000000000004</v>
       </c>
       <c r="L25" s="0">
-        <v>29.82</v>
+        <v>31.25</v>
       </c>
       <c r="M25" s="0">
-        <v>0.072999999999999995</v>
+        <v>0.080000000000000002</v>
       </c>
     </row>
     <row r="26">
@@ -1253,40 +1262,40 @@
         <v>25</v>
       </c>
       <c r="B26" s="0">
-        <v>26611986471</v>
+        <v>31121347333</v>
       </c>
       <c r="C26" s="0">
-        <v>30820516159</v>
+        <v>36745876431</v>
       </c>
       <c r="D26" s="0">
-        <v>1038777</v>
+        <v>867876</v>
       </c>
       <c r="E26" s="0">
-        <v>202</v>
+        <v>179</v>
       </c>
       <c r="F26" s="0">
-        <v>47236</v>
+        <v>136119</v>
       </c>
       <c r="G26" s="0">
-        <v>1.5900000000000001</v>
+        <v>3.21</v>
       </c>
       <c r="H26" s="0">
-        <v>11.210000000000001</v>
+        <v>11.92</v>
       </c>
       <c r="I26" s="0">
-        <v>86.349999999999994</v>
+        <v>84.689999999999998</v>
       </c>
       <c r="J26" s="0">
-        <v>3261</v>
+        <v>1512</v>
       </c>
       <c r="K26" s="0">
-        <v>8594.7800000000007</v>
+        <v>4467.9300000000003</v>
       </c>
       <c r="L26" s="0">
-        <v>42.939999999999998</v>
+        <v>25.02</v>
       </c>
       <c r="M26" s="0">
-        <v>0.092999999999999999</v>
+        <v>0.060999999999999999</v>
       </c>
     </row>
     <row r="27">
@@ -1294,40 +1303,40 @@
         <v>26</v>
       </c>
       <c r="B27" s="0">
-        <v>14053041227</v>
+        <v>27270675985</v>
       </c>
       <c r="C27" s="0">
-        <v>16727373751</v>
+        <v>31340900942</v>
       </c>
       <c r="D27" s="0">
-        <v>1250177</v>
+        <v>619141</v>
       </c>
       <c r="E27" s="0">
-        <v>234</v>
+        <v>188</v>
       </c>
       <c r="F27" s="0">
-        <v>19598</v>
+        <v>148345</v>
       </c>
       <c r="G27" s="0">
-        <v>1.46</v>
+        <v>2.9300000000000002</v>
       </c>
       <c r="H27" s="0">
-        <v>11.300000000000001</v>
+        <v>8.6600000000000001</v>
       </c>
       <c r="I27" s="0">
-        <v>84.010000000000005</v>
+        <v>87.010000000000005</v>
       </c>
       <c r="J27" s="0">
-        <v>3643</v>
+        <v>1152</v>
       </c>
       <c r="K27" s="0">
-        <v>9589.7600000000002</v>
+        <v>6615.04</v>
       </c>
       <c r="L27" s="0">
-        <v>40.920000000000002</v>
+        <v>35.869999999999997</v>
       </c>
       <c r="M27" s="0">
-        <v>0.086999999999999994</v>
+        <v>0.092999999999999999</v>
       </c>
     </row>
     <row r="28">
@@ -1335,40 +1344,40 @@
         <v>27</v>
       </c>
       <c r="B28" s="0">
-        <v>16436017503</v>
+        <v>10190157103</v>
       </c>
       <c r="C28" s="0">
-        <v>19694143083</v>
+        <v>11723378333</v>
       </c>
       <c r="D28" s="0">
-        <v>1547065</v>
+        <v>873575</v>
       </c>
       <c r="E28" s="0">
-        <v>263</v>
+        <v>234</v>
       </c>
       <c r="F28" s="0">
-        <v>21969</v>
+        <v>34773</v>
       </c>
       <c r="G28" s="0">
-        <v>1.73</v>
+        <v>2.5899999999999999</v>
       </c>
       <c r="H28" s="0">
-        <v>12.58</v>
+        <v>9.1500000000000004</v>
       </c>
       <c r="I28" s="0">
-        <v>83.459999999999994</v>
+        <v>86.920000000000002</v>
       </c>
       <c r="J28" s="0">
-        <v>3442</v>
+        <v>1441</v>
       </c>
       <c r="K28" s="0">
-        <v>9671.6100000000006</v>
+        <v>6976.7600000000002</v>
       </c>
       <c r="L28" s="0">
-        <v>37.079999999999998</v>
+        <v>29.82</v>
       </c>
       <c r="M28" s="0">
-        <v>0.079000000000000001</v>
+        <v>0.072999999999999995</v>
       </c>
     </row>
     <row r="29">
@@ -1376,40 +1385,40 @@
         <v>28</v>
       </c>
       <c r="B29" s="0">
-        <v>17782793623</v>
+        <v>26611986471</v>
       </c>
       <c r="C29" s="0">
-        <v>20859053979</v>
+        <v>30820516159</v>
       </c>
       <c r="D29" s="0">
-        <v>1869091</v>
+        <v>1038777</v>
       </c>
       <c r="E29" s="0">
-        <v>282</v>
+        <v>202</v>
       </c>
       <c r="F29" s="0">
-        <v>17648</v>
+        <v>47236</v>
       </c>
       <c r="G29" s="0">
-        <v>1.5800000000000001</v>
+        <v>1.5900000000000001</v>
       </c>
       <c r="H29" s="0">
-        <v>13.720000000000001</v>
+        <v>11.210000000000001</v>
       </c>
       <c r="I29" s="0">
-        <v>85.25</v>
+        <v>86.349999999999994</v>
       </c>
       <c r="J29" s="0">
-        <v>4195</v>
+        <v>3261</v>
       </c>
       <c r="K29" s="0">
-        <v>9703.9500000000007</v>
+        <v>8594.7800000000007</v>
       </c>
       <c r="L29" s="0">
-        <v>34.439999999999998</v>
+        <v>42.939999999999998</v>
       </c>
       <c r="M29" s="0">
-        <v>0.070999999999999994</v>
+        <v>0.092999999999999999</v>
       </c>
     </row>
     <row r="30">
@@ -1417,40 +1426,40 @@
         <v>29</v>
       </c>
       <c r="B30" s="0">
-        <v>12759197716</v>
+        <v>14053041227</v>
       </c>
       <c r="C30" s="0">
-        <v>15531091188</v>
+        <v>16727373751</v>
       </c>
       <c r="D30" s="0">
-        <v>1891729</v>
+        <v>1250177</v>
       </c>
       <c r="E30" s="0">
-        <v>281</v>
+        <v>234</v>
       </c>
       <c r="F30" s="0">
-        <v>12014</v>
+        <v>19598</v>
       </c>
       <c r="G30" s="0">
         <v>1.46</v>
       </c>
       <c r="H30" s="0">
-        <v>13.91</v>
+        <v>11.300000000000001</v>
       </c>
       <c r="I30" s="0">
-        <v>82.150000000000006</v>
+        <v>84.010000000000005</v>
       </c>
       <c r="J30" s="0">
-        <v>4605</v>
+        <v>3643</v>
       </c>
       <c r="K30" s="0">
-        <v>9330.6800000000003</v>
+        <v>9589.7600000000002</v>
       </c>
       <c r="L30" s="0">
-        <v>33.240000000000002</v>
+        <v>40.920000000000002</v>
       </c>
       <c r="M30" s="0">
-        <v>0.069000000000000006</v>
+        <v>0.086999999999999994</v>
       </c>
     </row>
     <row r="31">
@@ -1458,40 +1467,40 @@
         <v>30</v>
       </c>
       <c r="B31" s="0">
-        <v>16804402831</v>
+        <v>16436017503</v>
       </c>
       <c r="C31" s="0">
-        <v>20504977586</v>
+        <v>19694143083</v>
       </c>
       <c r="D31" s="0">
-        <v>2034224</v>
+        <v>1547065</v>
       </c>
       <c r="E31" s="0">
-        <v>315</v>
+        <v>263</v>
       </c>
       <c r="F31" s="0">
-        <v>12085</v>
+        <v>21969</v>
       </c>
       <c r="G31" s="0">
-        <v>1.2</v>
+        <v>1.73</v>
       </c>
       <c r="H31" s="0">
-        <v>12.91</v>
+        <v>12.58</v>
       </c>
       <c r="I31" s="0">
-        <v>81.950000000000003</v>
+        <v>83.459999999999994</v>
       </c>
       <c r="J31" s="0">
-        <v>5421</v>
+        <v>3442</v>
       </c>
       <c r="K31" s="0">
-        <v>10282.190000000001</v>
+        <v>9671.6100000000006</v>
       </c>
       <c r="L31" s="0">
-        <v>32.850000000000001</v>
+        <v>37.079999999999998</v>
       </c>
       <c r="M31" s="0">
-        <v>0.065000000000000002</v>
+        <v>0.079000000000000001</v>
       </c>
     </row>
     <row r="32">
@@ -1499,40 +1508,40 @@
         <v>31</v>
       </c>
       <c r="B32" s="0">
-        <v>20413854016</v>
+        <v>17782793623</v>
       </c>
       <c r="C32" s="0">
-        <v>24045935719</v>
+        <v>20859053979</v>
       </c>
       <c r="D32" s="0">
-        <v>1382745</v>
+        <v>1869091</v>
       </c>
       <c r="E32" s="0">
-        <v>236</v>
+        <v>282</v>
       </c>
       <c r="F32" s="0">
-        <v>24916</v>
+        <v>17648</v>
       </c>
       <c r="G32" s="0">
-        <v>1.4299999999999999</v>
+        <v>1.5800000000000001</v>
       </c>
       <c r="H32" s="0">
-        <v>11.779999999999999</v>
+        <v>13.720000000000001</v>
       </c>
       <c r="I32" s="0">
-        <v>84.900000000000006</v>
+        <v>85.25</v>
       </c>
       <c r="J32" s="0">
-        <v>4091</v>
+        <v>4195</v>
       </c>
       <c r="K32" s="0">
-        <v>11826.639999999999</v>
+        <v>9703.9500000000007</v>
       </c>
       <c r="L32" s="0">
-        <v>50.130000000000003</v>
+        <v>34.439999999999998</v>
       </c>
       <c r="M32" s="0">
-        <v>0.10100000000000001</v>
+        <v>0.070999999999999994</v>
       </c>
     </row>
     <row r="33">
@@ -1540,40 +1549,40 @@
         <v>32</v>
       </c>
       <c r="B33" s="0">
-        <v>32165933845</v>
+        <v>12759197716</v>
       </c>
       <c r="C33" s="0">
-        <v>39193909732</v>
+        <v>15531091188</v>
       </c>
       <c r="D33" s="0">
-        <v>1789676</v>
+        <v>1891729</v>
       </c>
       <c r="E33" s="0">
-        <v>268</v>
+        <v>281</v>
       </c>
       <c r="F33" s="0">
-        <v>28722</v>
+        <v>12014</v>
       </c>
       <c r="G33" s="0">
-        <v>1.3100000000000001</v>
+        <v>1.46</v>
       </c>
       <c r="H33" s="0">
-        <v>13.289999999999999</v>
+        <v>13.91</v>
       </c>
       <c r="I33" s="0">
-        <v>82.069999999999993</v>
+        <v>82.150000000000006</v>
       </c>
       <c r="J33" s="0">
-        <v>5125</v>
+        <v>4605</v>
       </c>
       <c r="K33" s="0">
-        <v>11055.360000000001</v>
+        <v>9330.6800000000003</v>
       </c>
       <c r="L33" s="0">
-        <v>41.490000000000002</v>
+        <v>33.240000000000002</v>
       </c>
       <c r="M33" s="0">
-        <v>0.082000000000000003</v>
+        <v>0.069000000000000006</v>
       </c>
     </row>
     <row r="34">
@@ -1581,40 +1590,40 @@
         <v>33</v>
       </c>
       <c r="B34" s="0">
-        <v>13602227910</v>
+        <v>16804402831</v>
       </c>
       <c r="C34" s="0">
-        <v>15899831778</v>
+        <v>20504977586</v>
       </c>
       <c r="D34" s="0">
-        <v>2094839</v>
+        <v>2034224</v>
       </c>
       <c r="E34" s="0">
-        <v>318</v>
+        <v>315</v>
       </c>
       <c r="F34" s="0">
-        <v>11785</v>
+        <v>12085</v>
       </c>
       <c r="G34" s="0">
-        <v>1.55</v>
+        <v>1.2</v>
       </c>
       <c r="H34" s="0">
-        <v>13.24</v>
+        <v>12.91</v>
       </c>
       <c r="I34" s="0">
-        <v>85.549999999999997</v>
+        <v>81.950000000000003</v>
       </c>
       <c r="J34" s="0">
-        <v>4243</v>
+        <v>5421</v>
       </c>
       <c r="K34" s="0">
-        <v>9695.5699999999997</v>
+        <v>10282.190000000001</v>
       </c>
       <c r="L34" s="0">
-        <v>30.489999999999998</v>
+        <v>32.850000000000001</v>
       </c>
       <c r="M34" s="0">
-        <v>0.060999999999999999</v>
+        <v>0.065000000000000002</v>
       </c>
     </row>
     <row r="35">
@@ -1622,40 +1631,40 @@
         <v>34</v>
       </c>
       <c r="B35" s="0">
-        <v>55046861752</v>
+        <v>20413854016</v>
       </c>
       <c r="C35" s="0">
-        <v>67222585980</v>
+        <v>24045935719</v>
       </c>
       <c r="D35" s="0">
-        <v>1521906</v>
+        <v>1382745</v>
       </c>
       <c r="E35" s="0">
-        <v>296</v>
+        <v>236</v>
       </c>
       <c r="F35" s="0">
-        <v>64789</v>
+        <v>24916</v>
       </c>
       <c r="G35" s="0">
-        <v>1.47</v>
+        <v>1.4299999999999999</v>
       </c>
       <c r="H35" s="0">
-        <v>10.98</v>
+        <v>11.779999999999999</v>
       </c>
       <c r="I35" s="0">
-        <v>81.890000000000001</v>
+        <v>84.900000000000006</v>
       </c>
       <c r="J35" s="0">
-        <v>3620</v>
+        <v>4091</v>
       </c>
       <c r="K35" s="0">
-        <v>12821.780000000001</v>
+        <v>11826.639999999999</v>
       </c>
       <c r="L35" s="0">
-        <v>44.579999999999998</v>
+        <v>50.130000000000003</v>
       </c>
       <c r="M35" s="0">
-        <v>0.092999999999999999</v>
+        <v>0.10100000000000001</v>
       </c>
     </row>
     <row r="36">
@@ -1663,40 +1672,40 @@
         <v>35</v>
       </c>
       <c r="B36" s="0">
-        <v>24814388925</v>
+        <v>32165933845</v>
       </c>
       <c r="C36" s="0">
-        <v>31020857567</v>
+        <v>39193909732</v>
       </c>
       <c r="D36" s="0">
-        <v>2027507</v>
+        <v>1789676</v>
       </c>
       <c r="E36" s="0">
-        <v>329</v>
+        <v>268</v>
       </c>
       <c r="F36" s="0">
-        <v>19311</v>
+        <v>28722</v>
       </c>
       <c r="G36" s="0">
-        <v>1.26</v>
+        <v>1.3100000000000001</v>
       </c>
       <c r="H36" s="0">
-        <v>12.32</v>
+        <v>13.289999999999999</v>
       </c>
       <c r="I36" s="0">
-        <v>79.989999999999995</v>
+        <v>82.069999999999993</v>
       </c>
       <c r="J36" s="0">
-        <v>4881</v>
+        <v>5125</v>
       </c>
       <c r="K36" s="0">
-        <v>14456.959999999999</v>
+        <v>11055.360000000001</v>
       </c>
       <c r="L36" s="0">
-        <v>43.969999999999999</v>
+        <v>41.490000000000002</v>
       </c>
       <c r="M36" s="0">
-        <v>0.087999999999999995</v>
+        <v>0.082000000000000003</v>
       </c>
     </row>
     <row r="37">
@@ -1704,40 +1713,163 @@
         <v>36</v>
       </c>
       <c r="B37" s="0">
-        <v>1075495737674</v>
+        <v>13602227910</v>
       </c>
       <c r="C37" s="0">
-        <v>1290645368239</v>
+        <v>15899831778</v>
       </c>
       <c r="D37" s="0">
-        <v>556946</v>
+        <v>2094839</v>
       </c>
       <c r="E37" s="0">
+        <v>318</v>
+      </c>
+      <c r="F37" s="0">
+        <v>11785</v>
+      </c>
+      <c r="G37" s="0">
+        <v>1.55</v>
+      </c>
+      <c r="H37" s="0">
+        <v>13.24</v>
+      </c>
+      <c r="I37" s="0">
+        <v>85.549999999999997</v>
+      </c>
+      <c r="J37" s="0">
+        <v>4243</v>
+      </c>
+      <c r="K37" s="0">
+        <v>9695.5699999999997</v>
+      </c>
+      <c r="L37" s="0">
+        <v>30.489999999999998</v>
+      </c>
+      <c r="M37" s="0">
+        <v>0.060999999999999999</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="0" t="s">
+        <v>37</v>
+      </c>
+      <c r="B38" s="0">
+        <v>55046861752</v>
+      </c>
+      <c r="C38" s="0">
+        <v>67222585980</v>
+      </c>
+      <c r="D38" s="0">
+        <v>1521906</v>
+      </c>
+      <c r="E38" s="0">
+        <v>296</v>
+      </c>
+      <c r="F38" s="0">
+        <v>64789</v>
+      </c>
+      <c r="G38" s="0">
+        <v>1.47</v>
+      </c>
+      <c r="H38" s="0">
+        <v>10.98</v>
+      </c>
+      <c r="I38" s="0">
+        <v>81.890000000000001</v>
+      </c>
+      <c r="J38" s="0">
+        <v>3620</v>
+      </c>
+      <c r="K38" s="0">
+        <v>12821.780000000001</v>
+      </c>
+      <c r="L38" s="0">
+        <v>44.579999999999998</v>
+      </c>
+      <c r="M38" s="0">
+        <v>0.092999999999999999</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="0" t="s">
+        <v>38</v>
+      </c>
+      <c r="B39" s="0">
+        <v>24814388925</v>
+      </c>
+      <c r="C39" s="0">
+        <v>31020857567</v>
+      </c>
+      <c r="D39" s="0">
+        <v>2027507</v>
+      </c>
+      <c r="E39" s="0">
+        <v>329</v>
+      </c>
+      <c r="F39" s="0">
+        <v>19311</v>
+      </c>
+      <c r="G39" s="0">
+        <v>1.26</v>
+      </c>
+      <c r="H39" s="0">
+        <v>12.32</v>
+      </c>
+      <c r="I39" s="0">
+        <v>79.989999999999995</v>
+      </c>
+      <c r="J39" s="0">
+        <v>4881</v>
+      </c>
+      <c r="K39" s="0">
+        <v>14456.959999999999</v>
+      </c>
+      <c r="L39" s="0">
+        <v>43.969999999999999</v>
+      </c>
+      <c r="M39" s="0">
+        <v>0.087999999999999995</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="0" t="s">
+        <v>39</v>
+      </c>
+      <c r="B40" s="0">
+        <v>1077363406650</v>
+      </c>
+      <c r="C40" s="0">
+        <v>1293045243125</v>
+      </c>
+      <c r="D40" s="0">
+        <v>557941</v>
+      </c>
+      <c r="E40" s="0">
         <v>144</v>
       </c>
-      <c r="F37" s="0">
-        <v>8038577</v>
-      </c>
-      <c r="G37" s="0">
-        <v>3.4700000000000002</v>
-      </c>
-      <c r="H37" s="0">
-        <v>8.8200000000000003</v>
-      </c>
-      <c r="I37" s="0">
-        <v>83.329999999999998</v>
-      </c>
-      <c r="J37" s="0">
-        <v>937</v>
-      </c>
-      <c r="K37" s="0">
-        <v>5468.8299999999999</v>
-      </c>
-      <c r="L37" s="0">
-        <v>33.640000000000001</v>
-      </c>
-      <c r="M37" s="0">
-        <v>0.086999999999999994</v>
+      <c r="F40" s="0">
+        <v>8056937</v>
+      </c>
+      <c r="G40" s="0">
+        <v>3.48</v>
+      </c>
+      <c r="H40" s="0">
+        <v>8.8300000000000001</v>
+      </c>
+      <c r="I40" s="0">
+        <v>83.319999999999993</v>
+      </c>
+      <c r="J40" s="0">
+        <v>936</v>
+      </c>
+      <c r="K40" s="0">
+        <v>5459.0799999999999</v>
+      </c>
+      <c r="L40" s="0">
+        <v>33.579999999999998</v>
+      </c>
+      <c r="M40" s="0">
+        <v>0.085999999999999993</v>
       </c>
     </row>
   </sheetData>

--- a/Output Data Tables/APAT Outputs/Aggregated Tables/2023/Aircraft_Cumulative_Statistics_2023.xlsx
+++ b/Output Data Tables/APAT Outputs/Aggregated Tables/2023/Aircraft_Cumulative_Statistics_2023.xlsx
@@ -13,38 +13,11 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="52" uniqueCount="52">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="40" uniqueCount="40">
   <si>
     <t>Row</t>
   </si>
   <si>
-    <t>E145</t>
-  </si>
-  <si>
-    <t>CRJ-200</t>
-  </si>
-  <si>
-    <t>E170</t>
-  </si>
-  <si>
-    <t>E175</t>
-  </si>
-  <si>
-    <t>Q400</t>
-  </si>
-  <si>
-    <t>CRJ-550</t>
-  </si>
-  <si>
-    <t>CRJ-700</t>
-  </si>
-  <si>
-    <t>E190</t>
-  </si>
-  <si>
-    <t>CRJ-900</t>
-  </si>
-  <si>
     <t>A220-100</t>
   </si>
   <si>
@@ -57,22 +30,13 @@
     <t>A320</t>
   </si>
   <si>
-    <t>A320NEO</t>
-  </si>
-  <si>
     <t>A321</t>
   </si>
   <si>
     <t>A321NEO</t>
   </si>
   <si>
-    <t>MD-80</t>
-  </si>
-  <si>
     <t>B717-200</t>
-  </si>
-  <si>
-    <t>B737-400</t>
   </si>
   <si>
     <t>B737-700</t>
@@ -214,7 +178,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:M40"/>
+  <dimension ref="A1:M28"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="11.140625" customWidth="true"/>
@@ -237,40 +201,40 @@
         <v>0</v>
       </c>
       <c r="B1" s="0" t="s">
-        <v>40</v>
+        <v>28</v>
       </c>
       <c r="C1" s="0" t="s">
-        <v>41</v>
+        <v>29</v>
       </c>
       <c r="D1" s="0" t="s">
-        <v>42</v>
+        <v>30</v>
       </c>
       <c r="E1" s="0" t="s">
-        <v>43</v>
+        <v>31</v>
       </c>
       <c r="F1" s="0" t="s">
-        <v>44</v>
+        <v>32</v>
       </c>
       <c r="G1" s="0" t="s">
-        <v>45</v>
+        <v>33</v>
       </c>
       <c r="H1" s="0" t="s">
-        <v>46</v>
+        <v>34</v>
       </c>
       <c r="I1" s="0" t="s">
-        <v>47</v>
+        <v>35</v>
       </c>
       <c r="J1" s="0" t="s">
-        <v>48</v>
+        <v>36</v>
       </c>
       <c r="K1" s="0" t="s">
-        <v>49</v>
+        <v>37</v>
       </c>
       <c r="L1" s="0" t="s">
-        <v>50</v>
+        <v>38</v>
       </c>
       <c r="M1" s="0" t="s">
-        <v>51</v>
+        <v>39</v>
       </c>
     </row>
     <row r="2">
@@ -278,40 +242,40 @@
         <v>1</v>
       </c>
       <c r="B2" s="0">
-        <v>2678843025</v>
+        <v>5042223818</v>
       </c>
       <c r="C2" s="0">
-        <v>3164679184</v>
+        <v>5940796394</v>
       </c>
       <c r="D2" s="0">
-        <v>66751</v>
+        <v>366716</v>
       </c>
       <c r="E2" s="0">
-        <v>50</v>
+        <v>109</v>
       </c>
       <c r="F2" s="0">
-        <v>188384</v>
+        <v>58208</v>
       </c>
       <c r="G2" s="0">
-        <v>3.9700000000000002</v>
+        <v>3.5899999999999999</v>
       </c>
       <c r="H2" s="0">
-        <v>5.8700000000000001</v>
+        <v>9.4800000000000004</v>
       </c>
       <c r="I2" s="0">
-        <v>84.650000000000006</v>
+        <v>84.870000000000005</v>
       </c>
       <c r="J2" s="0">
-        <v>336</v>
+        <v>937</v>
       </c>
       <c r="K2" s="0">
-        <v>2050.8800000000001</v>
+        <v>4983.1599999999999</v>
       </c>
       <c r="L2" s="0">
-        <v>41.020000000000003</v>
+        <v>45.729999999999997</v>
       </c>
       <c r="M2" s="0">
-        <v>0.17999999999999999</v>
+        <v>0.129</v>
       </c>
     </row>
     <row r="3">
@@ -319,40 +283,40 @@
         <v>2</v>
       </c>
       <c r="B3" s="0">
-        <v>1611785435</v>
+        <v>2469175191</v>
       </c>
       <c r="C3" s="0">
-        <v>2115281440</v>
+        <v>2927271422</v>
       </c>
       <c r="D3" s="0">
-        <v>36208</v>
+        <v>475979</v>
       </c>
       <c r="E3" s="0">
-        <v>50</v>
+        <v>130</v>
       </c>
       <c r="F3" s="0">
-        <v>126026</v>
+        <v>22230</v>
       </c>
       <c r="G3" s="0">
-        <v>2.1600000000000001</v>
+        <v>3.6099999999999999</v>
       </c>
       <c r="H3" s="0">
-        <v>3.0299999999999998</v>
+        <v>9.8100000000000005</v>
       </c>
       <c r="I3" s="0">
-        <v>76.200000000000003</v>
+        <v>84.349999999999994</v>
       </c>
       <c r="J3" s="0">
-        <v>336</v>
+        <v>1013</v>
       </c>
       <c r="K3" s="0">
-        <v>2480.46</v>
+        <v>5177.75</v>
       </c>
       <c r="L3" s="0">
-        <v>49.609999999999999</v>
+        <v>39.829999999999998</v>
       </c>
       <c r="M3" s="0">
-        <v>0.20799999999999999</v>
+        <v>0.107</v>
       </c>
     </row>
     <row r="4">
@@ -360,40 +324,40 @@
         <v>3</v>
       </c>
       <c r="B4" s="0">
-        <v>1685606282</v>
+        <v>30917589495</v>
       </c>
       <c r="C4" s="0">
-        <v>2002685392</v>
+        <v>37189389329</v>
       </c>
       <c r="D4" s="0">
-        <v>57681</v>
+        <v>379445</v>
       </c>
       <c r="E4" s="0">
-        <v>68</v>
+        <v>128</v>
       </c>
       <c r="F4" s="0">
-        <v>62276</v>
+        <v>380540</v>
       </c>
       <c r="G4" s="0">
-        <v>1.79</v>
+        <v>3.8799999999999999</v>
       </c>
       <c r="H4" s="0">
-        <v>3.1699999999999999</v>
+        <v>8.6300000000000008</v>
       </c>
       <c r="I4" s="0">
-        <v>84.170000000000002</v>
+        <v>83.140000000000001</v>
       </c>
       <c r="J4" s="0">
-        <v>475</v>
+        <v>762</v>
       </c>
       <c r="K4" s="0">
-        <v>1884.53</v>
+        <v>5306.5600000000004</v>
       </c>
       <c r="L4" s="0">
-        <v>27.82</v>
+        <v>41.380000000000003</v>
       </c>
       <c r="M4" s="0">
-        <v>0.104</v>
+        <v>0.121</v>
       </c>
     </row>
     <row r="5">
@@ -401,40 +365,40 @@
         <v>4</v>
       </c>
       <c r="B5" s="0">
-        <v>31343967901</v>
+        <v>28750016865</v>
       </c>
       <c r="C5" s="0">
-        <v>38536746923</v>
+        <v>34454797803</v>
       </c>
       <c r="D5" s="0">
-        <v>128808</v>
+        <v>465920</v>
       </c>
       <c r="E5" s="0">
-        <v>75</v>
+        <v>152</v>
       </c>
       <c r="F5" s="0">
-        <v>997537</v>
+        <v>277160</v>
       </c>
       <c r="G5" s="0">
-        <v>3.3300000000000001</v>
+        <v>3.75</v>
       </c>
       <c r="H5" s="0">
-        <v>5.9699999999999998</v>
+        <v>8.6699999999999999</v>
       </c>
       <c r="I5" s="0">
-        <v>81.340000000000003</v>
+        <v>83.439999999999998</v>
       </c>
       <c r="J5" s="0">
-        <v>514</v>
+        <v>817</v>
       </c>
       <c r="K5" s="0">
-        <v>1692.8299999999999</v>
+        <v>5700.5100000000002</v>
       </c>
       <c r="L5" s="0">
-        <v>22.550000000000001</v>
+        <v>37.460000000000001</v>
       </c>
       <c r="M5" s="0">
-        <v>0.079000000000000001</v>
+        <v>0.106</v>
       </c>
     </row>
     <row r="6">
@@ -442,40 +406,40 @@
         <v>5</v>
       </c>
       <c r="B6" s="0">
-        <v>5360970</v>
+        <v>80165713648</v>
       </c>
       <c r="C6" s="0">
-        <v>6834452</v>
+        <v>93286008291</v>
       </c>
       <c r="D6" s="0">
-        <v>40203</v>
+        <v>746527</v>
       </c>
       <c r="E6" s="0">
-        <v>76</v>
+        <v>188</v>
       </c>
       <c r="F6" s="0">
-        <v>509</v>
+        <v>470923</v>
       </c>
       <c r="G6" s="0">
-        <v>2.9900000000000002</v>
+        <v>3.77</v>
       </c>
       <c r="H6" s="0">
-        <v>2.9399999999999999</v>
+        <v>10.67</v>
       </c>
       <c r="I6" s="0">
-        <v>78.439999999999998</v>
+        <v>85.939999999999998</v>
       </c>
       <c r="J6" s="0">
-        <v>177</v>
+        <v>1073</v>
       </c>
       <c r="K6" s="0">
-        <v>27362</v>
+        <v>6442.1499999999996</v>
       </c>
       <c r="L6" s="0">
-        <v>360.02999999999997</v>
+        <v>34.780000000000001</v>
       </c>
       <c r="M6" s="0">
-        <v>2.0019999999999998</v>
+        <v>0.091999999999999998</v>
       </c>
     </row>
     <row r="7">
@@ -483,40 +447,40 @@
         <v>6</v>
       </c>
       <c r="B7" s="0">
-        <v>606963891</v>
+        <v>35076045297</v>
       </c>
       <c r="C7" s="0">
-        <v>735124450</v>
+        <v>40610824711</v>
       </c>
       <c r="D7" s="0">
-        <v>30066</v>
+        <v>1053732</v>
       </c>
       <c r="E7" s="0">
-        <v>50</v>
+        <v>195</v>
       </c>
       <c r="F7" s="0">
-        <v>45438</v>
+        <v>113312</v>
       </c>
       <c r="G7" s="0">
-        <v>1.8600000000000001</v>
+        <v>2.9399999999999999</v>
       </c>
       <c r="H7" s="0">
-        <v>2.8100000000000001</v>
+        <v>12.69</v>
       </c>
       <c r="I7" s="0">
-        <v>82.569999999999993</v>
+        <v>86.370000000000005</v>
       </c>
       <c r="J7" s="0">
-        <v>324</v>
+        <v>1835</v>
       </c>
       <c r="K7" s="0">
-        <v>2810.73</v>
+        <v>6713.5900000000001</v>
       </c>
       <c r="L7" s="0">
-        <v>56.210000000000001</v>
+        <v>34.380000000000003</v>
       </c>
       <c r="M7" s="0">
-        <v>0.26200000000000001</v>
+        <v>0.081000000000000003</v>
       </c>
     </row>
     <row r="8">
@@ -524,40 +488,40 @@
         <v>7</v>
       </c>
       <c r="B8" s="0">
-        <v>4811058348</v>
+        <v>5589093674</v>
       </c>
       <c r="C8" s="0">
-        <v>6121509112</v>
+        <v>6515587898</v>
       </c>
       <c r="D8" s="0">
-        <v>89222</v>
+        <v>255513</v>
       </c>
       <c r="E8" s="0">
-        <v>66</v>
+        <v>110</v>
       </c>
       <c r="F8" s="0">
-        <v>216349</v>
+        <v>129410</v>
       </c>
       <c r="G8" s="0">
-        <v>3.1499999999999999</v>
+        <v>5.0700000000000003</v>
       </c>
       <c r="H8" s="0">
-        <v>5.0800000000000001</v>
+        <v>7.7000000000000002</v>
       </c>
       <c r="I8" s="0">
-        <v>78.590000000000003</v>
+        <v>85.780000000000001</v>
       </c>
       <c r="J8" s="0">
-        <v>428</v>
+        <v>458</v>
       </c>
       <c r="K8" s="0">
-        <v>2567.5900000000001</v>
+        <v>5248.8100000000004</v>
       </c>
       <c r="L8" s="0">
-        <v>38.890000000000001</v>
+        <v>47.719999999999999</v>
       </c>
       <c r="M8" s="0">
-        <v>0.14599999999999999</v>
+        <v>0.158</v>
       </c>
     </row>
     <row r="9">
@@ -565,40 +529,40 @@
         <v>8</v>
       </c>
       <c r="B9" s="0">
-        <v>3328424207</v>
+        <v>4633653379</v>
       </c>
       <c r="C9" s="0">
-        <v>4120279832</v>
+        <v>5416511436</v>
       </c>
       <c r="D9" s="0">
-        <v>236119</v>
+        <v>370994</v>
       </c>
       <c r="E9" s="0">
-        <v>101</v>
+        <v>126</v>
       </c>
       <c r="F9" s="0">
-        <v>81316</v>
+        <v>46259</v>
       </c>
       <c r="G9" s="0">
-        <v>4.6600000000000001</v>
+        <v>3.1699999999999999</v>
       </c>
       <c r="H9" s="0">
-        <v>8.3399999999999999</v>
+        <v>8.2699999999999996</v>
       </c>
       <c r="I9" s="0">
-        <v>80.780000000000001</v>
+        <v>85.549999999999997</v>
       </c>
       <c r="J9" s="0">
-        <v>503</v>
+        <v>929</v>
       </c>
       <c r="K9" s="0">
-        <v>5513.1599999999999</v>
+        <v>7781.96</v>
       </c>
       <c r="L9" s="0">
-        <v>54.789999999999999</v>
+        <v>61.759999999999998</v>
       </c>
       <c r="M9" s="0">
-        <v>0.19500000000000001</v>
+        <v>0.17399999999999999</v>
       </c>
     </row>
     <row r="10">
@@ -606,40 +570,40 @@
         <v>9</v>
       </c>
       <c r="B10" s="0">
-        <v>10990857295</v>
+        <v>87507095851</v>
       </c>
       <c r="C10" s="0">
-        <v>13435631377</v>
+        <v>104172205914</v>
       </c>
       <c r="D10" s="0">
-        <v>145156</v>
+        <v>550768</v>
       </c>
       <c r="E10" s="0">
-        <v>75</v>
+        <v>169</v>
       </c>
       <c r="F10" s="0">
-        <v>415846</v>
+        <v>653173</v>
       </c>
       <c r="G10" s="0">
-        <v>4.4900000000000002</v>
+        <v>3.4500000000000002</v>
       </c>
       <c r="H10" s="0">
-        <v>7.2699999999999996</v>
+        <v>8.9900000000000002</v>
       </c>
       <c r="I10" s="0">
-        <v>81.799999999999997</v>
+        <v>84</v>
       </c>
       <c r="J10" s="0">
-        <v>429</v>
+        <v>946</v>
       </c>
       <c r="K10" s="0">
-        <v>2096.96</v>
+        <v>5704.6199999999999</v>
       </c>
       <c r="L10" s="0">
-        <v>27.82</v>
+        <v>33.840000000000003</v>
       </c>
       <c r="M10" s="0">
-        <v>0.105</v>
+        <v>0.092999999999999999</v>
       </c>
     </row>
     <row r="11">
@@ -647,40 +611,40 @@
         <v>10</v>
       </c>
       <c r="B11" s="0">
-        <v>5042223818</v>
+        <v>23187347124</v>
       </c>
       <c r="C11" s="0">
-        <v>5940796394</v>
+        <v>26952964500</v>
       </c>
       <c r="D11" s="0">
-        <v>366716</v>
+        <v>702632</v>
       </c>
       <c r="E11" s="0">
-        <v>109</v>
+        <v>169</v>
       </c>
       <c r="F11" s="0">
-        <v>58208</v>
+        <v>127200</v>
       </c>
       <c r="G11" s="0">
-        <v>3.5899999999999999</v>
+        <v>3.3199999999999998</v>
       </c>
       <c r="H11" s="0">
-        <v>9.4800000000000004</v>
+        <v>10.710000000000001</v>
       </c>
       <c r="I11" s="0">
-        <v>84.870000000000005</v>
+        <v>86.030000000000001</v>
       </c>
       <c r="J11" s="0">
-        <v>937</v>
+        <v>1256</v>
       </c>
       <c r="K11" s="0">
-        <v>4983.1599999999999</v>
+        <v>5323.6999999999998</v>
       </c>
       <c r="L11" s="0">
-        <v>45.729999999999997</v>
+        <v>31.559999999999999</v>
       </c>
       <c r="M11" s="0">
-        <v>0.129</v>
+        <v>0.081000000000000003</v>
       </c>
     </row>
     <row r="12">
@@ -688,40 +652,40 @@
         <v>11</v>
       </c>
       <c r="B12" s="0">
-        <v>7165334582</v>
+        <v>2114871868</v>
       </c>
       <c r="C12" s="0">
-        <v>8777447933</v>
+        <v>2562888527</v>
       </c>
       <c r="D12" s="0">
-        <v>707288</v>
+        <v>585134</v>
       </c>
       <c r="E12" s="0">
-        <v>134</v>
+        <v>179</v>
       </c>
       <c r="F12" s="0">
-        <v>58569</v>
+        <v>15843</v>
       </c>
       <c r="G12" s="0">
-        <v>4.7199999999999998</v>
+        <v>3.6200000000000001</v>
       </c>
       <c r="H12" s="0">
-        <v>14</v>
+        <v>8.9700000000000006</v>
       </c>
       <c r="I12" s="0">
-        <v>81.629999999999995</v>
+        <v>82.519999999999996</v>
       </c>
       <c r="J12" s="0">
-        <v>1114</v>
+        <v>904</v>
       </c>
       <c r="K12" s="0">
-        <v>3835.1799999999998</v>
+        <v>5328.25</v>
       </c>
       <c r="L12" s="0">
-        <v>28.5</v>
+        <v>29.77</v>
       </c>
       <c r="M12" s="0">
-        <v>0.075999999999999998</v>
+        <v>0.082000000000000003</v>
       </c>
     </row>
     <row r="13">
@@ -729,40 +693,40 @@
         <v>12</v>
       </c>
       <c r="B13" s="0">
-        <v>38332240832</v>
+        <v>60896033857</v>
       </c>
       <c r="C13" s="0">
-        <v>45966398192</v>
+        <v>70200931050</v>
       </c>
       <c r="D13" s="0">
-        <v>385592</v>
+        <v>648088</v>
       </c>
       <c r="E13" s="0">
-        <v>132</v>
+        <v>179</v>
       </c>
       <c r="F13" s="0">
-        <v>446753</v>
+        <v>353814</v>
       </c>
       <c r="G13" s="0">
-        <v>3.75</v>
+        <v>3.27</v>
       </c>
       <c r="H13" s="0">
-        <v>8.4499999999999993</v>
+        <v>9.3599999999999994</v>
       </c>
       <c r="I13" s="0">
-        <v>83.390000000000001</v>
+        <v>86.75</v>
       </c>
       <c r="J13" s="0">
-        <v>780</v>
+        <v>1106</v>
       </c>
       <c r="K13" s="0">
-        <v>5238.4399999999996</v>
+        <v>5752.4899999999998</v>
       </c>
       <c r="L13" s="0">
-        <v>39.780000000000001</v>
+        <v>32.079999999999998</v>
       </c>
       <c r="M13" s="0">
-        <v>0.115</v>
+        <v>0.083000000000000004</v>
       </c>
     </row>
     <row r="14">
@@ -770,40 +734,40 @@
         <v>13</v>
       </c>
       <c r="B14" s="0">
-        <v>83263671726</v>
+        <v>16847530748</v>
       </c>
       <c r="C14" s="0">
-        <v>100304254392</v>
+        <v>19701008679</v>
       </c>
       <c r="D14" s="0">
-        <v>553311</v>
+        <v>817469</v>
       </c>
       <c r="E14" s="0">
-        <v>164</v>
+        <v>179</v>
       </c>
       <c r="F14" s="0">
-        <v>643900</v>
+        <v>78874</v>
       </c>
       <c r="G14" s="0">
-        <v>3.5499999999999998</v>
+        <v>3.27</v>
       </c>
       <c r="H14" s="0">
-        <v>9.1699999999999999</v>
+        <v>11.33</v>
       </c>
       <c r="I14" s="0">
-        <v>83.010000000000005</v>
+        <v>85.519999999999996</v>
       </c>
       <c r="J14" s="0">
-        <v>947</v>
+        <v>1395</v>
       </c>
       <c r="K14" s="0">
-        <v>5526.6899999999996</v>
+        <v>4732.5799999999999</v>
       </c>
       <c r="L14" s="0">
-        <v>33.659999999999997</v>
+        <v>26.440000000000001</v>
       </c>
       <c r="M14" s="0">
-        <v>0.091999999999999998</v>
+        <v>0.066000000000000003</v>
       </c>
     </row>
     <row r="15">
@@ -811,40 +775,40 @@
         <v>14</v>
       </c>
       <c r="B15" s="0">
-        <v>37390349543</v>
+        <v>27270675985</v>
       </c>
       <c r="C15" s="0">
-        <v>45247127300</v>
+        <v>31340900942</v>
       </c>
       <c r="D15" s="0">
-        <v>764310</v>
+        <v>619141</v>
       </c>
       <c r="E15" s="0">
-        <v>184</v>
+        <v>188</v>
       </c>
       <c r="F15" s="0">
-        <v>236739</v>
+        <v>148345</v>
       </c>
       <c r="G15" s="0">
-        <v>4</v>
+        <v>2.9300000000000002</v>
       </c>
       <c r="H15" s="0">
-        <v>11.19</v>
+        <v>8.6600000000000001</v>
       </c>
       <c r="I15" s="0">
-        <v>82.640000000000001</v>
+        <v>87.010000000000005</v>
       </c>
       <c r="J15" s="0">
-        <v>1038</v>
+        <v>1152</v>
       </c>
       <c r="K15" s="0">
-        <v>4660.0799999999999</v>
+        <v>6615.04</v>
       </c>
       <c r="L15" s="0">
-        <v>25.309999999999999</v>
+        <v>35.869999999999997</v>
       </c>
       <c r="M15" s="0">
-        <v>0.068000000000000005</v>
+        <v>0.092999999999999999</v>
       </c>
     </row>
     <row r="16">
@@ -852,40 +816,40 @@
         <v>15</v>
       </c>
       <c r="B16" s="0">
-        <v>112260940495</v>
+        <v>10190157103</v>
       </c>
       <c r="C16" s="0">
-        <v>132270457295</v>
+        <v>11723378333</v>
       </c>
       <c r="D16" s="0">
-        <v>796666</v>
+        <v>873575</v>
       </c>
       <c r="E16" s="0">
-        <v>192</v>
+        <v>234</v>
       </c>
       <c r="F16" s="0">
-        <v>609729</v>
+        <v>34773</v>
       </c>
       <c r="G16" s="0">
-        <v>3.6699999999999999</v>
+        <v>2.5899999999999999</v>
       </c>
       <c r="H16" s="0">
-        <v>11.06</v>
+        <v>9.1500000000000004</v>
       </c>
       <c r="I16" s="0">
-        <v>84.870000000000005</v>
+        <v>86.920000000000002</v>
       </c>
       <c r="J16" s="0">
-        <v>1156</v>
+        <v>1441</v>
       </c>
       <c r="K16" s="0">
-        <v>6012.0600000000004</v>
+        <v>6976.7600000000002</v>
       </c>
       <c r="L16" s="0">
-        <v>31.879999999999999</v>
+        <v>29.82</v>
       </c>
       <c r="M16" s="0">
-        <v>0.083000000000000004</v>
+        <v>0.072999999999999995</v>
       </c>
     </row>
     <row r="17">
@@ -893,40 +857,40 @@
         <v>16</v>
       </c>
       <c r="B17" s="0">
-        <v>52356590976</v>
+        <v>26611986471</v>
       </c>
       <c r="C17" s="0">
-        <v>62104598448</v>
+        <v>30820516159</v>
       </c>
       <c r="D17" s="0">
-        <v>976795</v>
+        <v>1038777</v>
       </c>
       <c r="E17" s="0">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="F17" s="0">
-        <v>175525</v>
+        <v>47236</v>
       </c>
       <c r="G17" s="0">
-        <v>2.7599999999999998</v>
+        <v>1.5900000000000001</v>
       </c>
       <c r="H17" s="0">
-        <v>11.82</v>
+        <v>11.210000000000001</v>
       </c>
       <c r="I17" s="0">
-        <v>84.299999999999997</v>
+        <v>86.349999999999994</v>
       </c>
       <c r="J17" s="0">
-        <v>1808</v>
+        <v>3261</v>
       </c>
       <c r="K17" s="0">
-        <v>6199.8599999999997</v>
+        <v>8594.4799999999996</v>
       </c>
       <c r="L17" s="0">
-        <v>31.57</v>
+        <v>42.939999999999998</v>
       </c>
       <c r="M17" s="0">
-        <v>0.074999999999999997</v>
+        <v>0.092999999999999999</v>
       </c>
     </row>
     <row r="18">
@@ -934,40 +898,40 @@
         <v>17</v>
       </c>
       <c r="B18" s="0">
-        <v>532585</v>
+        <v>14053041227</v>
       </c>
       <c r="C18" s="0">
-        <v>614200</v>
+        <v>16727373751</v>
       </c>
       <c r="D18" s="0">
-        <v>0</v>
+        <v>1250177</v>
       </c>
       <c r="E18" s="0">
-        <v>166</v>
+        <v>234</v>
       </c>
       <c r="F18" s="0">
-        <v>4</v>
+        <v>19598</v>
       </c>
       <c r="G18" s="0">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="H18" s="0">
-        <v>0</v>
+        <v>11.300000000000001</v>
       </c>
       <c r="I18" s="0">
-        <v>86.709999999999994</v>
+        <v>84.010000000000005</v>
       </c>
       <c r="J18" s="0">
-        <v>925</v>
+        <v>3643</v>
       </c>
       <c r="K18" s="0">
-        <v>0</v>
+        <v>9589.7600000000002</v>
       </c>
       <c r="L18" s="0">
-        <v>0</v>
+        <v>40.920000000000002</v>
       </c>
       <c r="M18" s="0">
-        <v>0</v>
+        <v>0.086999999999999994</v>
       </c>
     </row>
     <row r="19">
@@ -975,40 +939,40 @@
         <v>18</v>
       </c>
       <c r="B19" s="0">
-        <v>6343882022</v>
+        <v>4154951451</v>
       </c>
       <c r="C19" s="0">
-        <v>7530081594</v>
+        <v>5212985751</v>
       </c>
       <c r="D19" s="0">
-        <v>232123</v>
+        <v>1316411</v>
       </c>
       <c r="E19" s="0">
-        <v>116</v>
+        <v>222</v>
       </c>
       <c r="F19" s="0">
-        <v>186904</v>
+        <v>5680</v>
       </c>
       <c r="G19" s="0">
-        <v>5.7599999999999998</v>
+        <v>1.4299999999999999</v>
       </c>
       <c r="H19" s="0">
-        <v>7.4400000000000004</v>
+        <v>12.32</v>
       </c>
       <c r="I19" s="0">
-        <v>84.25</v>
+        <v>79.700000000000003</v>
       </c>
       <c r="J19" s="0">
-        <v>359</v>
+        <v>4142</v>
       </c>
       <c r="K19" s="0">
-        <v>5402.1599999999999</v>
+        <v>9570.9200000000001</v>
       </c>
       <c r="L19" s="0">
-        <v>47.659999999999997</v>
+        <v>43.189999999999998</v>
       </c>
       <c r="M19" s="0">
-        <v>0.17299999999999999</v>
+        <v>0.089999999999999997</v>
       </c>
     </row>
     <row r="20">
@@ -1016,40 +980,40 @@
         <v>19</v>
       </c>
       <c r="B20" s="0">
-        <v>2233015</v>
+        <v>17782793623</v>
       </c>
       <c r="C20" s="0">
-        <v>2829711</v>
+        <v>20859053979</v>
       </c>
       <c r="D20" s="0">
-        <v>0</v>
+        <v>1869091</v>
       </c>
       <c r="E20" s="0">
-        <v>127</v>
+        <v>282</v>
       </c>
       <c r="F20" s="0">
-        <v>23</v>
+        <v>17648</v>
       </c>
       <c r="G20" s="0">
-        <v>0</v>
+        <v>1.5800000000000001</v>
       </c>
       <c r="H20" s="0">
-        <v>0</v>
+        <v>13.720000000000001</v>
       </c>
       <c r="I20" s="0">
-        <v>78.909999999999997</v>
+        <v>85.25</v>
       </c>
       <c r="J20" s="0">
-        <v>948</v>
+        <v>4195</v>
       </c>
       <c r="K20" s="0">
-        <v>194001.29000000001</v>
+        <v>9703.9500000000007</v>
       </c>
       <c r="L20" s="0">
-        <v>1504.79</v>
+        <v>34.439999999999998</v>
       </c>
       <c r="M20" s="0">
-        <v>3.903</v>
+        <v>0.070999999999999994</v>
       </c>
     </row>
     <row r="21">
@@ -1057,40 +1021,40 @@
         <v>20</v>
       </c>
       <c r="B21" s="0">
-        <v>63600056469</v>
+        <v>12759197716</v>
       </c>
       <c r="C21" s="0">
-        <v>79362523702</v>
+        <v>15531091188</v>
       </c>
       <c r="D21" s="0">
-        <v>471022</v>
+        <v>1910343</v>
       </c>
       <c r="E21" s="0">
-        <v>142</v>
+        <v>281</v>
       </c>
       <c r="F21" s="0">
-        <v>824931</v>
+        <v>12014</v>
       </c>
       <c r="G21" s="0">
-        <v>4.9000000000000004</v>
+        <v>1.48</v>
       </c>
       <c r="H21" s="0">
-        <v>9.4100000000000001</v>
+        <v>14.050000000000001</v>
       </c>
       <c r="I21" s="0">
-        <v>80.140000000000001</v>
+        <v>82.150000000000006</v>
       </c>
       <c r="J21" s="0">
-        <v>680</v>
+        <v>4605</v>
       </c>
       <c r="K21" s="0">
-        <v>5058.04</v>
+        <v>9299.7000000000007</v>
       </c>
       <c r="L21" s="0">
-        <v>35.780000000000001</v>
+        <v>33.130000000000003</v>
       </c>
       <c r="M21" s="0">
-        <v>0.10100000000000001</v>
+        <v>0.068000000000000005</v>
       </c>
     </row>
     <row r="22">
@@ -1098,40 +1062,40 @@
         <v>21</v>
       </c>
       <c r="B22" s="0">
-        <v>147810541920</v>
+        <v>16804402831</v>
       </c>
       <c r="C22" s="0">
-        <v>179017007109</v>
+        <v>20504977586</v>
       </c>
       <c r="D22" s="0">
-        <v>584832</v>
+        <v>2034224</v>
       </c>
       <c r="E22" s="0">
-        <v>171</v>
+        <v>315</v>
       </c>
       <c r="F22" s="0">
-        <v>1150101</v>
+        <v>12085</v>
       </c>
       <c r="G22" s="0">
-        <v>3.7599999999999998</v>
+        <v>1.2</v>
       </c>
       <c r="H22" s="0">
-        <v>9.3200000000000003</v>
+        <v>12.91</v>
       </c>
       <c r="I22" s="0">
-        <v>82.569999999999993</v>
+        <v>81.950000000000003</v>
       </c>
       <c r="J22" s="0">
-        <v>914</v>
+        <v>5421</v>
       </c>
       <c r="K22" s="0">
-        <v>5456.1700000000001</v>
+        <v>10282.190000000001</v>
       </c>
       <c r="L22" s="0">
-        <v>32.030000000000001</v>
+        <v>32.850000000000001</v>
       </c>
       <c r="M22" s="0">
-        <v>0.086999999999999994</v>
+        <v>0.065000000000000002</v>
       </c>
     </row>
     <row r="23">
@@ -1139,40 +1103,40 @@
         <v>22</v>
       </c>
       <c r="B23" s="0">
-        <v>61324542034</v>
+        <v>20413854016</v>
       </c>
       <c r="C23" s="0">
-        <v>74285364300</v>
+        <v>24045935719</v>
       </c>
       <c r="D23" s="0">
-        <v>702595</v>
+        <v>1382745</v>
       </c>
       <c r="E23" s="0">
-        <v>173</v>
+        <v>236</v>
       </c>
       <c r="F23" s="0">
-        <v>453332</v>
+        <v>24916</v>
       </c>
       <c r="G23" s="0">
-        <v>4.29</v>
+        <v>1.4299999999999999</v>
       </c>
       <c r="H23" s="0">
-        <v>10.73</v>
+        <v>11.779999999999999</v>
       </c>
       <c r="I23" s="0">
-        <v>82.549999999999997</v>
+        <v>84.900000000000006</v>
       </c>
       <c r="J23" s="0">
-        <v>949</v>
+        <v>4091</v>
       </c>
       <c r="K23" s="0">
-        <v>4625.0699999999997</v>
+        <v>11826.639999999999</v>
       </c>
       <c r="L23" s="0">
-        <v>26.780000000000001</v>
+        <v>50.130000000000003</v>
       </c>
       <c r="M23" s="0">
-        <v>0.070999999999999994</v>
+        <v>0.10100000000000001</v>
       </c>
     </row>
     <row r="24">
@@ -1180,40 +1144,40 @@
         <v>23</v>
       </c>
       <c r="B24" s="0">
-        <v>4406467602</v>
+        <v>32165933845</v>
       </c>
       <c r="C24" s="0">
-        <v>5376305619</v>
+        <v>39193909732</v>
       </c>
       <c r="D24" s="0">
-        <v>613034</v>
+        <v>1789676</v>
       </c>
       <c r="E24" s="0">
-        <v>178</v>
+        <v>268</v>
       </c>
       <c r="F24" s="0">
-        <v>31870</v>
+        <v>28722</v>
       </c>
       <c r="G24" s="0">
-        <v>3.6299999999999999</v>
+        <v>1.3100000000000001</v>
       </c>
       <c r="H24" s="0">
-        <v>9.4299999999999997</v>
+        <v>13.289999999999999</v>
       </c>
       <c r="I24" s="0">
-        <v>81.959999999999994</v>
+        <v>82.069999999999993</v>
       </c>
       <c r="J24" s="0">
-        <v>945</v>
+        <v>5125</v>
       </c>
       <c r="K24" s="0">
-        <v>5259.8699999999999</v>
+        <v>11055.360000000001</v>
       </c>
       <c r="L24" s="0">
-        <v>29.469999999999999</v>
+        <v>41.490000000000002</v>
       </c>
       <c r="M24" s="0">
-        <v>0.081000000000000003</v>
+        <v>0.082000000000000003</v>
       </c>
     </row>
     <row r="25">
@@ -1221,40 +1185,40 @@
         <v>24</v>
       </c>
       <c r="B25" s="0">
-        <v>81928045437</v>
+        <v>13602227910</v>
       </c>
       <c r="C25" s="0">
-        <v>95290232546</v>
+        <v>15899831778</v>
       </c>
       <c r="D25" s="0">
-        <v>694738</v>
+        <v>2094839</v>
       </c>
       <c r="E25" s="0">
-        <v>179</v>
+        <v>318</v>
       </c>
       <c r="F25" s="0">
-        <v>447358</v>
+        <v>11785</v>
       </c>
       <c r="G25" s="0">
-        <v>3.2599999999999998</v>
+        <v>1.55</v>
       </c>
       <c r="H25" s="0">
-        <v>9.9299999999999997</v>
+        <v>13.24</v>
       </c>
       <c r="I25" s="0">
-        <v>85.980000000000004</v>
+        <v>85.549999999999997</v>
       </c>
       <c r="J25" s="0">
-        <v>1190</v>
+        <v>4243</v>
       </c>
       <c r="K25" s="0">
-        <v>5592.6000000000004</v>
+        <v>9681.8099999999995</v>
       </c>
       <c r="L25" s="0">
-        <v>31.25</v>
+        <v>30.449999999999999</v>
       </c>
       <c r="M25" s="0">
-        <v>0.080000000000000002</v>
+        <v>0.060999999999999999</v>
       </c>
     </row>
     <row r="26">
@@ -1262,40 +1226,40 @@
         <v>25</v>
       </c>
       <c r="B26" s="0">
-        <v>31121347333</v>
+        <v>55046861752</v>
       </c>
       <c r="C26" s="0">
-        <v>36745876431</v>
+        <v>67222585980</v>
       </c>
       <c r="D26" s="0">
-        <v>867876</v>
+        <v>1521906</v>
       </c>
       <c r="E26" s="0">
-        <v>179</v>
+        <v>296</v>
       </c>
       <c r="F26" s="0">
-        <v>136119</v>
+        <v>64789</v>
       </c>
       <c r="G26" s="0">
-        <v>3.21</v>
+        <v>1.47</v>
       </c>
       <c r="H26" s="0">
-        <v>11.92</v>
+        <v>10.98</v>
       </c>
       <c r="I26" s="0">
-        <v>84.689999999999998</v>
+        <v>81.890000000000001</v>
       </c>
       <c r="J26" s="0">
-        <v>1512</v>
+        <v>3620</v>
       </c>
       <c r="K26" s="0">
-        <v>4467.9300000000003</v>
+        <v>12821.780000000001</v>
       </c>
       <c r="L26" s="0">
-        <v>25.02</v>
+        <v>44.579999999999998</v>
       </c>
       <c r="M26" s="0">
-        <v>0.060999999999999999</v>
+        <v>0.092999999999999999</v>
       </c>
     </row>
     <row r="27">
@@ -1303,40 +1267,40 @@
         <v>26</v>
       </c>
       <c r="B27" s="0">
-        <v>27270675985</v>
+        <v>24814388925</v>
       </c>
       <c r="C27" s="0">
-        <v>31340900942</v>
+        <v>31020857567</v>
       </c>
       <c r="D27" s="0">
-        <v>619141</v>
+        <v>2027507</v>
       </c>
       <c r="E27" s="0">
-        <v>188</v>
+        <v>329</v>
       </c>
       <c r="F27" s="0">
-        <v>148345</v>
+        <v>19311</v>
       </c>
       <c r="G27" s="0">
-        <v>2.9300000000000002</v>
+        <v>1.26</v>
       </c>
       <c r="H27" s="0">
-        <v>8.6600000000000001</v>
+        <v>12.32</v>
       </c>
       <c r="I27" s="0">
-        <v>87.010000000000005</v>
+        <v>79.989999999999995</v>
       </c>
       <c r="J27" s="0">
-        <v>1152</v>
+        <v>4881</v>
       </c>
       <c r="K27" s="0">
-        <v>6615.04</v>
+        <v>14456.959999999999</v>
       </c>
       <c r="L27" s="0">
-        <v>35.869999999999997</v>
+        <v>43.969999999999999</v>
       </c>
       <c r="M27" s="0">
-        <v>0.092999999999999999</v>
+        <v>0.087999999999999995</v>
       </c>
     </row>
     <row r="28">
@@ -1344,532 +1308,40 @@
         <v>27</v>
       </c>
       <c r="B28" s="0">
-        <v>10190157103</v>
+        <v>658866863670</v>
       </c>
       <c r="C28" s="0">
-        <v>11723378333</v>
+        <v>780034584419</v>
       </c>
       <c r="D28" s="0">
-        <v>873575</v>
+        <v>773092</v>
       </c>
       <c r="E28" s="0">
-        <v>234</v>
+        <v>173</v>
       </c>
       <c r="F28" s="0">
-        <v>34773</v>
+        <v>3173848</v>
       </c>
       <c r="G28" s="0">
-        <v>2.5899999999999999</v>
+        <v>3.1499999999999999</v>
       </c>
       <c r="H28" s="0">
-        <v>9.1500000000000004</v>
+        <v>9.9499999999999993</v>
       </c>
       <c r="I28" s="0">
-        <v>86.920000000000002</v>
+        <v>84.469999999999999</v>
       </c>
       <c r="J28" s="0">
-        <v>1441</v>
+        <v>1259</v>
       </c>
       <c r="K28" s="0">
-        <v>6976.7600000000002</v>
+        <v>6999.1300000000001</v>
       </c>
       <c r="L28" s="0">
-        <v>29.82</v>
+        <v>36.960000000000001</v>
       </c>
       <c r="M28" s="0">
-        <v>0.072999999999999995</v>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="0" t="s">
-        <v>28</v>
-      </c>
-      <c r="B29" s="0">
-        <v>26611986471</v>
-      </c>
-      <c r="C29" s="0">
-        <v>30820516159</v>
-      </c>
-      <c r="D29" s="0">
-        <v>1038777</v>
-      </c>
-      <c r="E29" s="0">
-        <v>202</v>
-      </c>
-      <c r="F29" s="0">
-        <v>47236</v>
-      </c>
-      <c r="G29" s="0">
-        <v>1.5900000000000001</v>
-      </c>
-      <c r="H29" s="0">
-        <v>11.210000000000001</v>
-      </c>
-      <c r="I29" s="0">
-        <v>86.349999999999994</v>
-      </c>
-      <c r="J29" s="0">
-        <v>3261</v>
-      </c>
-      <c r="K29" s="0">
-        <v>8594.7800000000007</v>
-      </c>
-      <c r="L29" s="0">
-        <v>42.939999999999998</v>
-      </c>
-      <c r="M29" s="0">
-        <v>0.092999999999999999</v>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="0" t="s">
-        <v>29</v>
-      </c>
-      <c r="B30" s="0">
-        <v>14053041227</v>
-      </c>
-      <c r="C30" s="0">
-        <v>16727373751</v>
-      </c>
-      <c r="D30" s="0">
-        <v>1250177</v>
-      </c>
-      <c r="E30" s="0">
-        <v>234</v>
-      </c>
-      <c r="F30" s="0">
-        <v>19598</v>
-      </c>
-      <c r="G30" s="0">
-        <v>1.46</v>
-      </c>
-      <c r="H30" s="0">
-        <v>11.300000000000001</v>
-      </c>
-      <c r="I30" s="0">
-        <v>84.010000000000005</v>
-      </c>
-      <c r="J30" s="0">
-        <v>3643</v>
-      </c>
-      <c r="K30" s="0">
-        <v>9589.7600000000002</v>
-      </c>
-      <c r="L30" s="0">
-        <v>40.920000000000002</v>
-      </c>
-      <c r="M30" s="0">
-        <v>0.086999999999999994</v>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="0" t="s">
-        <v>30</v>
-      </c>
-      <c r="B31" s="0">
-        <v>16436017503</v>
-      </c>
-      <c r="C31" s="0">
-        <v>19694143083</v>
-      </c>
-      <c r="D31" s="0">
-        <v>1547065</v>
-      </c>
-      <c r="E31" s="0">
-        <v>263</v>
-      </c>
-      <c r="F31" s="0">
-        <v>21969</v>
-      </c>
-      <c r="G31" s="0">
-        <v>1.73</v>
-      </c>
-      <c r="H31" s="0">
-        <v>12.58</v>
-      </c>
-      <c r="I31" s="0">
-        <v>83.459999999999994</v>
-      </c>
-      <c r="J31" s="0">
-        <v>3442</v>
-      </c>
-      <c r="K31" s="0">
-        <v>9671.6100000000006</v>
-      </c>
-      <c r="L31" s="0">
-        <v>37.079999999999998</v>
-      </c>
-      <c r="M31" s="0">
-        <v>0.079000000000000001</v>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="0" t="s">
-        <v>31</v>
-      </c>
-      <c r="B32" s="0">
-        <v>17782793623</v>
-      </c>
-      <c r="C32" s="0">
-        <v>20859053979</v>
-      </c>
-      <c r="D32" s="0">
-        <v>1869091</v>
-      </c>
-      <c r="E32" s="0">
-        <v>282</v>
-      </c>
-      <c r="F32" s="0">
-        <v>17648</v>
-      </c>
-      <c r="G32" s="0">
-        <v>1.5800000000000001</v>
-      </c>
-      <c r="H32" s="0">
-        <v>13.720000000000001</v>
-      </c>
-      <c r="I32" s="0">
-        <v>85.25</v>
-      </c>
-      <c r="J32" s="0">
-        <v>4195</v>
-      </c>
-      <c r="K32" s="0">
-        <v>9703.9500000000007</v>
-      </c>
-      <c r="L32" s="0">
-        <v>34.439999999999998</v>
-      </c>
-      <c r="M32" s="0">
-        <v>0.070999999999999994</v>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="0" t="s">
-        <v>32</v>
-      </c>
-      <c r="B33" s="0">
-        <v>12759197716</v>
-      </c>
-      <c r="C33" s="0">
-        <v>15531091188</v>
-      </c>
-      <c r="D33" s="0">
-        <v>1891729</v>
-      </c>
-      <c r="E33" s="0">
-        <v>281</v>
-      </c>
-      <c r="F33" s="0">
-        <v>12014</v>
-      </c>
-      <c r="G33" s="0">
-        <v>1.46</v>
-      </c>
-      <c r="H33" s="0">
-        <v>13.91</v>
-      </c>
-      <c r="I33" s="0">
-        <v>82.150000000000006</v>
-      </c>
-      <c r="J33" s="0">
-        <v>4605</v>
-      </c>
-      <c r="K33" s="0">
-        <v>9330.6800000000003</v>
-      </c>
-      <c r="L33" s="0">
-        <v>33.240000000000002</v>
-      </c>
-      <c r="M33" s="0">
-        <v>0.069000000000000006</v>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="0" t="s">
-        <v>33</v>
-      </c>
-      <c r="B34" s="0">
-        <v>16804402831</v>
-      </c>
-      <c r="C34" s="0">
-        <v>20504977586</v>
-      </c>
-      <c r="D34" s="0">
-        <v>2034224</v>
-      </c>
-      <c r="E34" s="0">
-        <v>315</v>
-      </c>
-      <c r="F34" s="0">
-        <v>12085</v>
-      </c>
-      <c r="G34" s="0">
-        <v>1.2</v>
-      </c>
-      <c r="H34" s="0">
-        <v>12.91</v>
-      </c>
-      <c r="I34" s="0">
-        <v>81.950000000000003</v>
-      </c>
-      <c r="J34" s="0">
-        <v>5421</v>
-      </c>
-      <c r="K34" s="0">
-        <v>10282.190000000001</v>
-      </c>
-      <c r="L34" s="0">
-        <v>32.850000000000001</v>
-      </c>
-      <c r="M34" s="0">
-        <v>0.065000000000000002</v>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="0" t="s">
-        <v>34</v>
-      </c>
-      <c r="B35" s="0">
-        <v>20413854016</v>
-      </c>
-      <c r="C35" s="0">
-        <v>24045935719</v>
-      </c>
-      <c r="D35" s="0">
-        <v>1382745</v>
-      </c>
-      <c r="E35" s="0">
-        <v>236</v>
-      </c>
-      <c r="F35" s="0">
-        <v>24916</v>
-      </c>
-      <c r="G35" s="0">
-        <v>1.4299999999999999</v>
-      </c>
-      <c r="H35" s="0">
-        <v>11.779999999999999</v>
-      </c>
-      <c r="I35" s="0">
-        <v>84.900000000000006</v>
-      </c>
-      <c r="J35" s="0">
-        <v>4091</v>
-      </c>
-      <c r="K35" s="0">
-        <v>11826.639999999999</v>
-      </c>
-      <c r="L35" s="0">
-        <v>50.130000000000003</v>
-      </c>
-      <c r="M35" s="0">
-        <v>0.10100000000000001</v>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="0" t="s">
-        <v>35</v>
-      </c>
-      <c r="B36" s="0">
-        <v>32165933845</v>
-      </c>
-      <c r="C36" s="0">
-        <v>39193909732</v>
-      </c>
-      <c r="D36" s="0">
-        <v>1789676</v>
-      </c>
-      <c r="E36" s="0">
-        <v>268</v>
-      </c>
-      <c r="F36" s="0">
-        <v>28722</v>
-      </c>
-      <c r="G36" s="0">
-        <v>1.3100000000000001</v>
-      </c>
-      <c r="H36" s="0">
-        <v>13.289999999999999</v>
-      </c>
-      <c r="I36" s="0">
-        <v>82.069999999999993</v>
-      </c>
-      <c r="J36" s="0">
-        <v>5125</v>
-      </c>
-      <c r="K36" s="0">
-        <v>11055.360000000001</v>
-      </c>
-      <c r="L36" s="0">
-        <v>41.490000000000002</v>
-      </c>
-      <c r="M36" s="0">
-        <v>0.082000000000000003</v>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="0" t="s">
-        <v>36</v>
-      </c>
-      <c r="B37" s="0">
-        <v>13602227910</v>
-      </c>
-      <c r="C37" s="0">
-        <v>15899831778</v>
-      </c>
-      <c r="D37" s="0">
-        <v>2094839</v>
-      </c>
-      <c r="E37" s="0">
-        <v>318</v>
-      </c>
-      <c r="F37" s="0">
-        <v>11785</v>
-      </c>
-      <c r="G37" s="0">
-        <v>1.55</v>
-      </c>
-      <c r="H37" s="0">
-        <v>13.24</v>
-      </c>
-      <c r="I37" s="0">
-        <v>85.549999999999997</v>
-      </c>
-      <c r="J37" s="0">
-        <v>4243</v>
-      </c>
-      <c r="K37" s="0">
-        <v>9695.5699999999997</v>
-      </c>
-      <c r="L37" s="0">
-        <v>30.489999999999998</v>
-      </c>
-      <c r="M37" s="0">
-        <v>0.060999999999999999</v>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" s="0" t="s">
-        <v>37</v>
-      </c>
-      <c r="B38" s="0">
-        <v>55046861752</v>
-      </c>
-      <c r="C38" s="0">
-        <v>67222585980</v>
-      </c>
-      <c r="D38" s="0">
-        <v>1521906</v>
-      </c>
-      <c r="E38" s="0">
-        <v>296</v>
-      </c>
-      <c r="F38" s="0">
-        <v>64789</v>
-      </c>
-      <c r="G38" s="0">
-        <v>1.47</v>
-      </c>
-      <c r="H38" s="0">
-        <v>10.98</v>
-      </c>
-      <c r="I38" s="0">
-        <v>81.890000000000001</v>
-      </c>
-      <c r="J38" s="0">
-        <v>3620</v>
-      </c>
-      <c r="K38" s="0">
-        <v>12821.780000000001</v>
-      </c>
-      <c r="L38" s="0">
-        <v>44.579999999999998</v>
-      </c>
-      <c r="M38" s="0">
-        <v>0.092999999999999999</v>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" s="0" t="s">
-        <v>38</v>
-      </c>
-      <c r="B39" s="0">
-        <v>24814388925</v>
-      </c>
-      <c r="C39" s="0">
-        <v>31020857567</v>
-      </c>
-      <c r="D39" s="0">
-        <v>2027507</v>
-      </c>
-      <c r="E39" s="0">
-        <v>329</v>
-      </c>
-      <c r="F39" s="0">
-        <v>19311</v>
-      </c>
-      <c r="G39" s="0">
-        <v>1.26</v>
-      </c>
-      <c r="H39" s="0">
-        <v>12.32</v>
-      </c>
-      <c r="I39" s="0">
-        <v>79.989999999999995</v>
-      </c>
-      <c r="J39" s="0">
-        <v>4881</v>
-      </c>
-      <c r="K39" s="0">
-        <v>14456.959999999999</v>
-      </c>
-      <c r="L39" s="0">
-        <v>43.969999999999999</v>
-      </c>
-      <c r="M39" s="0">
-        <v>0.087999999999999995</v>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" s="0" t="s">
-        <v>39</v>
-      </c>
-      <c r="B40" s="0">
-        <v>1077363406650</v>
-      </c>
-      <c r="C40" s="0">
-        <v>1293045243125</v>
-      </c>
-      <c r="D40" s="0">
-        <v>557941</v>
-      </c>
-      <c r="E40" s="0">
-        <v>144</v>
-      </c>
-      <c r="F40" s="0">
-        <v>8056937</v>
-      </c>
-      <c r="G40" s="0">
-        <v>3.48</v>
-      </c>
-      <c r="H40" s="0">
-        <v>8.8300000000000001</v>
-      </c>
-      <c r="I40" s="0">
-        <v>83.319999999999993</v>
-      </c>
-      <c r="J40" s="0">
-        <v>936</v>
-      </c>
-      <c r="K40" s="0">
-        <v>5459.0799999999999</v>
-      </c>
-      <c r="L40" s="0">
-        <v>33.579999999999998</v>
-      </c>
-      <c r="M40" s="0">
-        <v>0.085999999999999993</v>
+        <v>0.089999999999999997</v>
       </c>
     </row>
   </sheetData>
